--- a/data/chat_british_taxonomy_template.xlsx
+++ b/data/chat_british_taxonomy_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ak/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95787175-14F6-1C4A-AEB1-B7EB9A173B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A028D37-A461-7B4C-BF98-C405D9C0AB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,10 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="1314">
-  <si>
-    <t>Bridgely — Taxonomy Template</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="1272">
   <si>
     <t>Fixed, founder-curated classification for the Debrief Tool and Scenario Practice</t>
   </si>
@@ -262,9 +259,6 @@
     <t>Approved</t>
   </si>
   <si>
-    <t>Cultural consensus — no independent citation to check; needs a real client case, not further AI search.</t>
-  </si>
-  <si>
     <t>WP-2-promotion-discussion-indirectness</t>
   </si>
   <si>
@@ -301,9 +295,6 @@
     <t>Separate the tone from the content — read the specific facts/actions stated, and ask HR or the manager directly what the practical next steps are.</t>
   </si>
   <si>
-    <t>Search-verified: matches ACAS standard disciplinary process (verbal/informal → first written 6mo → final written 12mo → dismissal).</t>
-  </si>
-  <si>
     <t>WP-4-deadline-reminder-escalation</t>
   </si>
   <si>
@@ -322,9 +313,6 @@
     <t>Treat any second follow-up on the same task as a priority signal, regardless of how mild the wording still sounds.</t>
   </si>
   <si>
-    <t>Search-verified: Confirmed: a 2023 Preply UK survey lists "just a gentle reminder" among the most-hated passive-aggressive office phrases.</t>
-  </si>
-  <si>
     <t>WP-5-team-ritual-participation</t>
   </si>
   <si>
@@ -361,9 +349,6 @@
     <t>Prepare 2-3 clear points before the appointment, and ask directly for a follow-up if more time is needed: "Could we book a longer appointment to go through this properly?"</t>
   </si>
   <si>
-    <t>Search-verified: 10-min standard confirmed; UK average ~9 minutes, shortest in Europe.</t>
-  </si>
-  <si>
     <t>HC-2-referral-wait-silence</t>
   </si>
   <si>
@@ -382,9 +367,6 @@
     <t>Call the GP surgery or hospital referral line directly to check status rather than assuming; this is normal and expected, not rude to ask.</t>
   </si>
   <si>
-    <t>Search-verified: 18-week RTT standard confirmed; added current (2026) performance — only ~65% actually met within 18 weeks.</t>
-  </si>
-  <si>
     <t>HL-1-landlord-vague-commitment</t>
   </si>
   <si>
@@ -493,9 +475,6 @@
     <t>When newly CC'd people appear, ask plainly: “Just flagging — is there a concern here I should be addressing directly?”</t>
   </si>
   <si>
-    <t>Search-verified: Confirmed: same Preply survey — 47% of UK respondents had been CC'd to a boss over a minor issue.</t>
-  </si>
-  <si>
     <t>WP-8-sorry-to-bother-request</t>
   </si>
   <si>
@@ -568,9 +547,6 @@
     <t>Ask directly: “Based on what I've told you, how urgent is this specifically?” rather than reading the standard safety list as a signal.</t>
   </si>
   <si>
-    <t>Search-verified: NHS 111 online confirmed algorithm-driven (~120 symptom topics), no diagnosis given, same callback queue as phone 111.</t>
-  </si>
-  <si>
     <t>HC-4-pharmacist-first-point-of-contact</t>
   </si>
   <si>
@@ -589,9 +565,6 @@
     <t>Treat a pharmacist referral as a genuine, appropriate option — and if symptoms persist after, that's the natural point to request a GP appointment.</t>
   </si>
   <si>
-    <t>Search-verified &amp; strengthened: NHS Pharmacy First (launched Jan 2024) covers 7 specific named conditions — row now names them.</t>
-  </si>
-  <si>
     <t>HC-5-patient-advocating-for-self</t>
   </si>
   <si>
@@ -646,9 +619,6 @@
     <t>After the questionnaire, ask directly: “Can we talk a bit more about what's actually going on, beyond these questions?”</t>
   </si>
   <si>
-    <t>Search-verified: PHQ-9 confirmed as the real, standard 9-item NHS depression screening tool (scored 0-27, ~2-3 minutes to complete).</t>
-  </si>
-  <si>
     <t>HL-3-inventory-check-in-formality</t>
   </si>
   <si>
@@ -685,9 +655,6 @@
     <t>Read the specific ground cited in a Section 8 notice carefully — since Section 21 no longer exists, a valid eviction always requires one now, and it's reasonable to seek advice (e.g. from Shelter) on whether the stated ground genuinely applies.</t>
   </si>
   <si>
-    <t>Search-verified: REWRITTEN — Section 21 'no-fault' evictions were abolished in England 1 May 2026 (Renters' Rights Act 2025); row now reflects Section 8.</t>
-  </si>
-  <si>
     <t>HL-5-deposit-protection-scheme-silence</t>
   </si>
   <si>
@@ -706,9 +673,6 @@
     <t>Ask directly and in writing within the first few weeks: “Could you send me the deposit protection scheme reference for my deposit?” — this is a standard, expected request, not an accusation.</t>
   </si>
   <si>
-    <t>Search-verified: 30-day rule confirmed (Housing Act 2004/Localism Act 2011); penalty for non-compliance is 1-3x the deposit, awarded by a court.</t>
-  </si>
-  <si>
     <t>HL-6-shared-house-kitchen-etiquette-notes</t>
   </si>
   <si>
@@ -799,9 +763,6 @@
     <t>Prepare 4-5 specific past examples in advance, structured as situation → task → action → result, ready to adapt to different competency questions.</t>
   </si>
   <si>
-    <t>Search-verified: STAR (Situation/Task/Action/Result) confirmed as the standard, widely-taught UK technique for competency-based interview questions.</t>
-  </si>
-  <si>
     <t>JS-6-notice-period-negotiation-norm</t>
   </si>
   <si>
@@ -820,9 +781,6 @@
     <t>State the real notice period plainly and, if genuinely relevant, add a brief note of enthusiasm: “My notice period is one month, but I'm very keen to start as soon as that allows.”</t>
   </si>
   <si>
-    <t>Search-verified: statutory minimums confirmed (employee resigning: 1 week flat; employer dismissing: 1 week/year up to 12 weeks) — contractual notice can be longer, never shorter.</t>
-  </si>
-  <si>
     <t>JS-7-networking-coffee-informality</t>
   </si>
   <si>
@@ -1039,9 +997,6 @@
     <t>Treat this phrase as a signal to acknowledge the oversight directly and act immediately: "Sorry, I missed that — on it now."</t>
   </si>
   <si>
-    <t>Search-verified: Confirmed: Preply 2023 survey — "per my last email" ranked the #1 most passive-aggressive UK office phrase (83%/42% stats added to row).</t>
-  </si>
-  <si>
     <t>WP-12-calendar-invite-formality</t>
   </si>
   <si>
@@ -1132,9 +1087,6 @@
     <t>Separate the format from the relationship — ask direct practical questions about process and timeline, and note that HR can be followed up with directly.</t>
   </si>
   <si>
-    <t>Search-verified: matches ACAS/gov.uk collective consultation rules; added current (April 2026) protective-award penalty figure.</t>
-  </si>
-  <si>
     <t>WP-17-lets-take-this-offline</t>
   </si>
   <si>
@@ -1171,9 +1123,6 @@
     <t>Ask directly what to watch for and when to return: "What specific signs would mean I should come back sooner than two weeks?"</t>
   </si>
   <si>
-    <t>Search-verified: 'watchful waiting' confirmed as a real, standard clinical term used in NICE/CKS primary care guidance for managing uncertain or self-limiting symptoms.</t>
-  </si>
-  <si>
     <t>HC-9-econsult-online-triage-form</t>
   </si>
   <si>
@@ -1192,9 +1141,6 @@
     <t>Use the online form as the primary channel and be specific and complete in it, since it's often triaged faster than expected.</t>
   </si>
   <si>
-    <t>Search-verified: consistent with the confirmed NHS shift toward mandatory online/digital triage before phone or in-person GP contact (same pattern confirmed for NHS 111 online).</t>
-  </si>
-  <si>
     <t>HC-10-same-day-urgent-only-gatekeeping</t>
   </si>
   <si>
@@ -1231,9 +1177,6 @@
     <t>It's acceptable to ask the desk for a rough update after a long wait: "Just checking I'm still in the queue — any sense of how much longer?"</t>
   </si>
   <si>
-    <t>Search-verified: 4-hour national A&amp;E target confirmed real; also confirmed performance has run well below the 95% target for years, so long non-urgent waits are the norm.</t>
-  </si>
-  <si>
     <t>HC-12-two-week-review-standard</t>
   </si>
   <si>
@@ -1270,9 +1213,6 @@
     <t>Answer the checklist questions honestly and use the visit to raise any specific worries directly, since the standard format doesn't prevent asking follow-up questions.</t>
   </si>
   <si>
-    <t>Search-verified &amp; strengthened: confirmed exactly 5 mandated Healthy Child Programme contacts, with real ages/stages now named in the row.</t>
-  </si>
-  <si>
     <t>HC-14-appointment-letter-postal-delay</t>
   </si>
   <si>
@@ -1381,9 +1321,6 @@
     <t>If disputing a deduction, explicitly reference the standard and the property's age/usage: "Given the carpet is seven years old, this mark falls under fair wear and tear, not damage."</t>
   </si>
   <si>
-    <t>Search-verified: confirmed as standard, consistently used terminology across all three government-approved deposit schemes (DPS, mydeposits, TDS).</t>
-  </si>
-  <si>
     <t>HL-10-right-to-rent-document-check</t>
   </si>
   <si>
@@ -1402,9 +1339,6 @@
     <t>Provide the requested documents promptly as a standard step, and note that a landlord who skips this check for anyone is actually the one breaking the rules.</t>
   </si>
   <si>
-    <t>Search-verified &amp; strengthened: confirmed current and mandatory (gov.uk guidance updated Aug 2026); new digital verification provider rules roll out autumn 2026; penalty added.</t>
-  </si>
-  <si>
     <t>HL-11-guarantor-requirement-no-uk-credit-history</t>
   </si>
   <si>
@@ -1441,9 +1375,6 @@
     <t>If income is close to the threshold, ask directly whether savings or a larger upfront payment can be offered as an alternative to meeting the multiplier exactly.</t>
   </si>
   <si>
-    <t>Search-verified &amp; strengthened: 30x rule confirmed as current industry standard; added a significant related legal protection from the Renters' Rights Act 2025 (benefits/children discrimination now unlawful).</t>
-  </si>
-  <si>
     <t>HL-13-hmo-licensing-silence</t>
   </si>
   <si>
@@ -1462,9 +1393,6 @@
     <t>For any shared house with three or more unrelated tenants, it's reasonable to ask directly and in writing: "Could you confirm this property's HMO licence details?"</t>
   </si>
   <si>
-    <t>Search-verified: mandatory licensing threshold (5+ tenants, 2+ households, shared facilities) confirmed current; many councils also run additional licensing for smaller HMOs; unlicensed letting is a criminal offence.</t>
-  </si>
-  <si>
     <t>HL-14-permitted-occupiers-clause</t>
   </si>
   <si>
@@ -1501,9 +1429,6 @@
     <t>Set a specific follow-up date when asking: "Could you let me know by [date] either way, since I need to plan my next steps?"</t>
   </si>
   <si>
-    <t>Search-verified: UPDATED — fixed-term tenancies (and their break clauses) were phased out from 1 May 2026; all tenancies are now periodic.</t>
-  </si>
-  <si>
     <t>HL-16-end-of-tenancy-cleaning-checklist</t>
   </si>
   <si>
@@ -1540,9 +1465,6 @@
     <t>Respond to the substance (the new figure and effective date) directly; if it seems above local market rent, a tenant can challenge it at the First-tier Tribunal (currently a £47 application fee) before the new rent takes effect.</t>
   </si>
   <si>
-    <t>Search-verified: UPDATED — confirmed current rules: Section 13 is now the sole route, capped once/52 weeks, 2 months' notice, Form 4A, £47 tribunal fee.</t>
-  </si>
-  <si>
     <t>JS-8-keep-cv-on-file-soft-rejection</t>
   </si>
   <si>
@@ -1597,9 +1519,6 @@
     <t>Provide the requested documents promptly as a routine step, the same as any other new hire would be asked to do.</t>
   </si>
   <si>
-    <t>Search-verified: confirmed mandatory for every hire regardless of nationality (singling out only 'foreign-looking' candidates is itself illegal); done before day one; penalties up to £45,000-60,000 per illegal worker.</t>
-  </si>
-  <si>
     <t>JS-11-one-way-video-interview-norm</t>
   </si>
   <si>
@@ -1942,9 +1861,6 @@
     <t>Use the DVLA's online status checker if concerned, and allow the stated processing window in full before assuming an issue and calling to check.</t>
   </si>
   <si>
-    <t>Search-verified: gov.uk confirms licence usually arrives within 3 weeks (contact DVLA if longer); failure to notify DVLA of an address change carries a fine of up to £1,000.</t>
-  </si>
-  <si>
     <t>AB-7-ni-number-application-wait</t>
   </si>
   <si>
@@ -1963,9 +1879,6 @@
     <t>Note the reference number given at application and only chase up if the wait significantly exceeds the stated standard timeframe, which is usually a matter of weeks.</t>
   </si>
   <si>
-    <t>Search-verified &amp; updated: current (2026) standard processing window confirmed as 4-8 weeks under DWP's digital service.</t>
-  </si>
-  <si>
     <t>AB-8-please-allow-28-days-boilerplate</t>
   </si>
   <si>
@@ -2074,9 +1987,6 @@
     <t>It's reasonable to decline the paid add-on and submit a standard application directly if the details have already been carefully checked.</t>
   </si>
   <si>
-    <t>Search-verified: confirmed current (gov.uk guidance updated March 2026) — £16 fee on top of the passport fee, reduces rejection risk but doesn't guarantee success, no refund if the application itself is rejected.</t>
-  </si>
-  <si>
     <t>AB-14-ombudsman-escalation-language</t>
   </si>
   <si>
@@ -2203,9 +2113,6 @@
     <t>Learn the specific citation style required (e.g. Harvard, APA) early and cite even paraphrased ideas, not just direct quotes, to avoid triggering the automated similarity checks.</t>
   </si>
   <si>
-    <t>Search-verified: Turnitin's near-universal UK university use confirmed; it produces a similarity %, but universities' own policies confirm a human academic must interpret the report — close paraphrasing is a specifically flagged match pattern.</t>
-  </si>
-  <si>
     <t>ED-5-personal-tutor-checkin-brevity</t>
   </si>
   <si>
@@ -2332,9 +2239,6 @@
     <t>Start the formal assessment request as early as possible given it can take time, and ask directly what interim support, if any, is available while the assessment is pending.</t>
   </si>
   <si>
-    <t>Search-verified &amp; flagged current: confirmed 6-week/16-week statutory timescales; also surfaced that England's SEND/EHCP system is under active 2026 reform — worth re-checking again as it rolls out.</t>
-  </si>
-  <si>
     <t>ED-12-headteacher-escalation-formality</t>
   </si>
   <si>
@@ -2767,9 +2671,6 @@
     <t>Tip around 10-12.5% at sit-down restaurants if service isn't already included, and don't feel obligated to tip at counters, cafes, or most takeaways.</t>
   </si>
   <si>
-    <t>Search-verified &amp; strengthened with real survey figures (OnBuy/OpenTable): ~9% average tip, tipping rate varies hugely by venue type (88% waiters vs 29% bar staff vs 19% Uber).</t>
-  </si>
-  <si>
     <t>MN-2-service-charge-auto-added-notice</t>
   </si>
   <si>
@@ -2788,9 +2689,6 @@
     <t>It's fine to simply pay the standard service charge in most cases; if service was genuinely poor, it's acceptable to politely ask for it to be removed or reduced.</t>
   </si>
   <si>
-    <t>Search-verified: UPDATED — Employment (Allocation of Tips) Act 2023 (in force since 1 Oct 2024) guarantees 100% of tips/service charge to staff.</t>
-  </si>
-  <si>
     <t>MN-3-splitting-bill-evenly-default</t>
   </si>
   <si>
@@ -2827,9 +2725,6 @@
     <t>Avoid asking directly about someone's salary; if the topic is genuinely relevant (e.g. negotiating a role), frame it around a range or market rate rather than a personal question.</t>
   </si>
   <si>
-    <t>Search-verified &amp; strengthened: Indeed survey data confirms this is one of the strongest UK workplace taboos (87%/84%/16% stats added).</t>
-  </si>
-  <si>
     <t>MN-5-borrowing-money-awkwardness-indirect-language</t>
   </si>
   <si>
@@ -2974,9 +2869,6 @@
     <t>Ask the bank directly to set up an arranged overdraft limit in advance if overdraft use is likely, since this generally comes with lower fees than going into an unarranged one unexpectedly.</t>
   </si>
   <si>
-    <t>Search-verified &amp; UPDATED — the row's original premise (different fee structures) was outdated: FCA rules from April 2020 banned banks charging higher fees for unarranged vs arranged overdrafts; both are now priced the same, only the interest rate itself (~35-40%) applies either way.</t>
-  </si>
-  <si>
     <t>MN-13-self-checkout-default-expectation</t>
   </si>
   <si>
@@ -3013,9 +2905,6 @@
     <t>Check current earnings against the current repayment threshold if a new deduction appears, and contact the Student Loans Company directly for specifics on the loan account rather than the employer.</t>
   </si>
   <si>
-    <t>Search-verified &amp; strengthened: exact current (2026/27) thresholds by plan added, confirmed via HMRC/payroll sources.</t>
-  </si>
-  <si>
     <t>MN-15-contactless-tap-default-payment-norm</t>
   </si>
   <si>
@@ -3070,9 +2959,6 @@
     <t>After any delay of 15 minutes or more, check the specific train operator's Delay Repay claim process online and submit a claim with the ticket and journey details.</t>
   </si>
   <si>
-    <t>Search-verified: Confirmed via National Rail/operator sources: 15/30/60-min tiers and 28-day claim window are accurate; note added.</t>
-  </si>
-  <si>
     <t>TR-2-quiet-coach-etiquette</t>
   </si>
   <si>
@@ -3181,9 +3067,6 @@
     <t>Always tap out at the end of every journey, and if a maximum fare is mistakenly charged, submit a fare correction request online with the specific journey details.</t>
   </si>
   <si>
-    <t>Search-verified: confirmed a genuinely large-scale issue (TfL collected roughly £365m over 6 years from incomplete-journey max fares); TfL now auto-corrects some forgotten taps and a manual refund claim remains available.</t>
-  </si>
-  <si>
     <t>TR-8-excuse-me-this-is-my-stop-navigating-crowd</t>
   </si>
   <si>
@@ -3256,9 +3139,6 @@
     <t>Practice the precise mirror-signal-manoeuvre sequence deliberately for the test itself, even if real-world driving afterward tends to be more relaxed about exact timing.</t>
   </si>
   <si>
-    <t>Search-verified: DVSA's official DL25 marking sheet confirmed to specifically score mirror-signal-manoeuvre (MSM) as a distinct fault category — among the most common reasons candidates fail.</t>
-  </si>
-  <si>
     <t>TR-12-road-rage-passive-restrained-norm</t>
   </si>
   <si>
@@ -3295,9 +3175,6 @@
     <t>Check a city's specific emission zone and congestion charge boundaries and rules online before driving into an unfamiliar UK city centre, since there's no in-the-moment warning.</t>
   </si>
   <si>
-    <t>Search-verified: ULEZ confirmed current — £12.50/day, covers nearly all Greater London boroughs (since Aug 2023), camera-enforced 24/7 except Christmas Day.</t>
-  </si>
-  <si>
     <t>TR-14-luggage-rack-space-etiquette</t>
   </si>
   <si>
@@ -3586,9 +3463,6 @@
     <t>Always carry bags and clean up immediately after a dog in any public space, regardless of how quiet or empty the area seems at the time.</t>
   </si>
   <si>
-    <t>Search-verified &amp; strengthened: confirmed fine amounts (£50-100 fixed penalty, up to £1,000 in court) under the Dogs (Fouling of Land) Act 1996.</t>
-  </si>
-  <si>
     <t>NB-13-recycling-sorting-strictness</t>
   </si>
   <si>
@@ -3949,9 +3823,6 @@
     <t>Have a UK debit or credit card's PIN memorized and ready before shopping, since chip-and-PIN (or contactless for smaller amounts) is the standard, essentially universal verification method.</t>
   </si>
   <si>
-    <t>Search-verified &amp; updated: FCA removed the fixed £100 contactless cap nationally from 19 March 2026 (bank-by-bank now); note added.</t>
-  </si>
-  <si>
     <t>CS-17-feedback-survey-email-routine-request</t>
   </si>
   <si>
@@ -3968,6 +3839,9 @@
   </si>
   <si>
     <t>Treat a feedback survey email as routine and optional — it's sent to essentially every customer automatically and doesn't indicate anything specific about that particular transaction.</t>
+  </si>
+  <si>
+    <t>Chat British — Taxonomy Template</t>
   </si>
 </sst>
 </file>
@@ -4418,12 +4292,12 @@
   <sheetData>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -4434,35 +4308,35 @@
     <row r="5" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3"/>
       <c r="B5" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3"/>
       <c r="B6" s="5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3"/>
       <c r="B7" s="5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3"/>
       <c r="B8" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -4476,259 +4350,259 @@
     <row r="13" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="14" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B15" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B17" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="22" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B23" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B24" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B25" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="30" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="31" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B31" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="36" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B37" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="2:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B39" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B41" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B42" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B43" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B46" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="47" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B47" s="8"/>
       <c r="C47" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="9"/>
       <c r="C48" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B49" s="3"/>
       <c r="C49" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" t="s">
         <v>46</v>
-      </c>
-      <c r="C52" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="53" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" t="s">
         <v>48</v>
-      </c>
-      <c r="C53" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="54" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
+        <v>49</v>
+      </c>
+      <c r="C54" t="s">
         <v>50</v>
-      </c>
-      <c r="C54" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="55" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
+        <v>51</v>
+      </c>
+      <c r="C55" t="s">
         <v>52</v>
-      </c>
-      <c r="C55" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="56" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" t="s">
         <v>54</v>
-      </c>
-      <c r="C56" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="57" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" t="s">
         <v>56</v>
-      </c>
-      <c r="C57" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="59" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4755,5832 +4629,5432 @@
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>76</v>
-      </c>
       <c r="H2" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" s="12" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I2" s="12"/>
     </row>
     <row r="3" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="F3" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="G3" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>84</v>
-      </c>
       <c r="H3" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>90</v>
-      </c>
       <c r="H4" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>91</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="F5" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="G5" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>97</v>
-      </c>
       <c r="H5" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I5" s="12" t="s">
-        <v>98</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I5" s="12"/>
     </row>
     <row r="6" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="G6" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="H6" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I6" s="12" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I6" s="12"/>
     </row>
     <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>110</v>
-      </c>
       <c r="H7" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I7" s="12" t="s">
-        <v>111</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I7" s="12"/>
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>117</v>
-      </c>
       <c r="H8" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I8" s="12" t="s">
-        <v>118</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:9" s="14" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" spans="1:9" s="14" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I10" s="13"/>
     </row>
     <row r="11" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I11" s="12"/>
     </row>
     <row r="12" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I12" s="12" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I12" s="12"/>
     </row>
     <row r="13" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I13" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>155</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I15" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I15" s="15"/>
     </row>
     <row r="16" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I17" s="15"/>
     </row>
     <row r="18" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I18" s="16" t="s">
-        <v>180</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I18" s="16"/>
     </row>
     <row r="19" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>187</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I20" s="16"/>
     </row>
     <row r="21" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I21" s="16"/>
     </row>
     <row r="22" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>206</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>219</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>226</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="G27" s="15" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="H28" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I28" s="16"/>
     </row>
     <row r="29" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I29" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I29" s="16"/>
     </row>
     <row r="30" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>257</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I30" s="16"/>
     </row>
     <row r="31" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>258</v>
+        <v>245</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>261</v>
+        <v>248</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I31" s="16" t="s">
-        <v>264</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I31" s="16"/>
     </row>
     <row r="32" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>269</v>
+        <v>255</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>270</v>
+        <v>256</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I32" s="16"/>
     </row>
     <row r="33" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>272</v>
+        <v>258</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>273</v>
+        <v>259</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I33" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I34" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I34" s="15"/>
     </row>
     <row r="35" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I35" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="C36" s="15" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I36" s="15"/>
     </row>
     <row r="37" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I37" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I37" s="15"/>
     </row>
     <row r="38" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I38" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I38" s="16"/>
     </row>
     <row r="39" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I39" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I39" s="16"/>
     </row>
     <row r="40" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I40" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I40" s="16"/>
     </row>
     <row r="41" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>320</v>
+        <v>306</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="H41" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I41" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I41" s="16"/>
     </row>
     <row r="42" spans="1:9" s="17" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>328</v>
+        <v>314</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I42" s="16" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I42" s="16"/>
     </row>
     <row r="43" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>332</v>
+        <v>318</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>334</v>
+        <v>320</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="G43" s="15" t="s">
-        <v>336</v>
+        <v>322</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I43" s="15" t="s">
-        <v>337</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I43" s="15"/>
     </row>
     <row r="44" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C44" s="15" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="D44" s="15" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="E44" s="15" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="G44" s="15" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I44" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I44" s="15"/>
     </row>
     <row r="45" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="G45" s="15" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I45" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I45" s="15"/>
     </row>
     <row r="46" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C46" s="15" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="G46" s="15" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I46" s="15"/>
     </row>
     <row r="47" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="G47" s="15" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I47" s="15"/>
     </row>
     <row r="48" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="C48" s="15" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="D48" s="15" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="G48" s="15" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I48" s="15" t="s">
-        <v>368</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I48" s="15"/>
     </row>
     <row r="49" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="D49" s="15" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="G49" s="15" t="s">
-        <v>374</v>
+        <v>358</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I49" s="15"/>
     </row>
     <row r="50" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="F50" s="15" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="G50" s="15" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>381</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I50" s="15"/>
     </row>
     <row r="51" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="G51" s="15" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="H51" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I51" s="15" t="s">
-        <v>388</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I51" s="15"/>
     </row>
     <row r="52" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="C52" s="15" t="s">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="D52" s="15" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="G52" s="15" t="s">
-        <v>394</v>
+        <v>376</v>
       </c>
       <c r="H52" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I52" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I52" s="15"/>
     </row>
     <row r="53" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="C53" s="15" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="D53" s="15" t="s">
-        <v>397</v>
+        <v>379</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="F53" s="15" t="s">
-        <v>399</v>
+        <v>381</v>
       </c>
       <c r="G53" s="15" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
       <c r="H53" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I53" s="15" t="s">
-        <v>401</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I53" s="15"/>
     </row>
     <row r="54" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="C54" s="15" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="G54" s="15" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="H54" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I54" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I54" s="15"/>
     </row>
     <row r="55" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="G55" s="15" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I55" s="15" t="s">
-        <v>414</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I55" s="15"/>
     </row>
     <row r="56" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="D56" s="15" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="G56" s="15" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I56" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I56" s="15"/>
     </row>
     <row r="57" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="C57" s="15" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="D57" s="15" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="G57" s="15" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I57" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I57" s="15"/>
     </row>
     <row r="58" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="E58" s="15" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="G58" s="15" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I58" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I58" s="15"/>
     </row>
     <row r="59" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="E59" s="15" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="G59" s="15" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I59" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I59" s="15"/>
     </row>
     <row r="60" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="D60" s="15" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="G60" s="15" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I60" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I60" s="15"/>
     </row>
     <row r="61" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="G61" s="15" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I61" s="15" t="s">
-        <v>451</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I61" s="15"/>
     </row>
     <row r="62" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="C62" s="15" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="D62" s="15" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="F62" s="15" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="G62" s="15" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="H62" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I62" s="15" t="s">
-        <v>458</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I62" s="15"/>
     </row>
     <row r="63" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="E63" s="15" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="G63" s="15" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="H63" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I63" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I63" s="15"/>
     </row>
     <row r="64" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="G64" s="15" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="H64" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I64" s="15" t="s">
-        <v>471</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I64" s="15"/>
     </row>
     <row r="65" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>472</v>
+        <v>449</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>473</v>
+        <v>450</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>474</v>
+        <v>451</v>
       </c>
       <c r="E65" s="15" t="s">
-        <v>475</v>
+        <v>452</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>476</v>
+        <v>453</v>
       </c>
       <c r="G65" s="15" t="s">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="H65" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I65" s="15" t="s">
-        <v>478</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I65" s="15"/>
     </row>
     <row r="66" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="G66" s="15" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="H66" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I66" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I66" s="15"/>
     </row>
     <row r="67" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
       <c r="C67" s="15" t="s">
-        <v>486</v>
+        <v>462</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>487</v>
+        <v>463</v>
       </c>
       <c r="E67" s="15" t="s">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="G67" s="15" t="s">
-        <v>490</v>
+        <v>466</v>
       </c>
       <c r="H67" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I67" s="15" t="s">
-        <v>491</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I67" s="15"/>
     </row>
     <row r="68" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="D68" s="15" t="s">
-        <v>494</v>
+        <v>469</v>
       </c>
       <c r="E68" s="15" t="s">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="H68" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I68" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I68" s="15"/>
     </row>
     <row r="69" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B69" s="15" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="C69" s="15" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
       <c r="D69" s="15" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I69" s="15" t="s">
-        <v>504</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I69" s="15"/>
     </row>
     <row r="70" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>505</v>
+        <v>479</v>
       </c>
       <c r="C70" s="15" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="D70" s="15" t="s">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="H70" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I70" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I70" s="15"/>
     </row>
     <row r="71" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B71" s="15" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="C71" s="15" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
       <c r="D71" s="15" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I71" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I71" s="15"/>
     </row>
     <row r="72" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c r="H72" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I72" s="15" t="s">
-        <v>523</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I72" s="15"/>
     </row>
     <row r="73" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B73" s="15" t="s">
-        <v>524</v>
+        <v>497</v>
       </c>
       <c r="C73" s="15" t="s">
-        <v>525</v>
+        <v>498</v>
       </c>
       <c r="D73" s="15" t="s">
-        <v>526</v>
+        <v>499</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>527</v>
+        <v>500</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>528</v>
+        <v>501</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>529</v>
+        <v>502</v>
       </c>
       <c r="H73" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I73" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I73" s="15"/>
     </row>
     <row r="74" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>530</v>
+        <v>503</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>531</v>
+        <v>504</v>
       </c>
       <c r="D74" s="15" t="s">
-        <v>532</v>
+        <v>505</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>533</v>
+        <v>506</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>534</v>
+        <v>507</v>
       </c>
       <c r="G74" s="15" t="s">
-        <v>535</v>
+        <v>508</v>
       </c>
       <c r="H74" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I74" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I74" s="15"/>
     </row>
     <row r="75" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B75" s="15" t="s">
-        <v>536</v>
+        <v>509</v>
       </c>
       <c r="C75" s="15" t="s">
-        <v>537</v>
+        <v>510</v>
       </c>
       <c r="D75" s="15" t="s">
-        <v>538</v>
+        <v>511</v>
       </c>
       <c r="E75" s="15" t="s">
-        <v>539</v>
+        <v>512</v>
       </c>
       <c r="F75" s="15" t="s">
-        <v>540</v>
+        <v>513</v>
       </c>
       <c r="G75" s="15" t="s">
-        <v>541</v>
+        <v>514</v>
       </c>
       <c r="H75" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I75" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I75" s="15"/>
     </row>
     <row r="76" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>542</v>
+        <v>515</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>543</v>
+        <v>516</v>
       </c>
       <c r="D76" s="15" t="s">
-        <v>544</v>
+        <v>517</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>545</v>
+        <v>518</v>
       </c>
       <c r="F76" s="15" t="s">
-        <v>546</v>
+        <v>519</v>
       </c>
       <c r="G76" s="15" t="s">
-        <v>547</v>
+        <v>520</v>
       </c>
       <c r="H76" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I76" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I76" s="15"/>
     </row>
     <row r="77" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B77" s="15" t="s">
-        <v>548</v>
+        <v>521</v>
       </c>
       <c r="C77" s="15" t="s">
-        <v>549</v>
+        <v>522</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>550</v>
+        <v>523</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>551</v>
+        <v>524</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>552</v>
+        <v>525</v>
       </c>
       <c r="G77" s="15" t="s">
-        <v>553</v>
+        <v>526</v>
       </c>
       <c r="H77" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I77" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I77" s="15"/>
     </row>
     <row r="78" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B78" s="15" t="s">
-        <v>554</v>
+        <v>527</v>
       </c>
       <c r="C78" s="15" t="s">
-        <v>555</v>
+        <v>528</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>556</v>
+        <v>529</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>557</v>
+        <v>530</v>
       </c>
       <c r="F78" s="15" t="s">
-        <v>558</v>
+        <v>531</v>
       </c>
       <c r="G78" s="15" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
       <c r="H78" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I78" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I78" s="15"/>
     </row>
     <row r="79" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B79" s="15" t="s">
-        <v>560</v>
+        <v>533</v>
       </c>
       <c r="C79" s="15" t="s">
-        <v>561</v>
+        <v>534</v>
       </c>
       <c r="D79" s="15" t="s">
-        <v>562</v>
+        <v>535</v>
       </c>
       <c r="E79" s="15" t="s">
-        <v>563</v>
+        <v>536</v>
       </c>
       <c r="F79" s="15" t="s">
-        <v>564</v>
+        <v>537</v>
       </c>
       <c r="G79" s="15" t="s">
-        <v>565</v>
+        <v>538</v>
       </c>
       <c r="H79" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I79" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I79" s="15"/>
     </row>
     <row r="80" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>566</v>
+        <v>539</v>
       </c>
       <c r="C80" s="15" t="s">
-        <v>567</v>
+        <v>540</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>568</v>
+        <v>541</v>
       </c>
       <c r="E80" s="15" t="s">
-        <v>569</v>
+        <v>542</v>
       </c>
       <c r="F80" s="15" t="s">
-        <v>570</v>
+        <v>543</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>571</v>
+        <v>544</v>
       </c>
       <c r="H80" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I80" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I80" s="15"/>
     </row>
     <row r="81" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B81" s="15" t="s">
-        <v>572</v>
+        <v>545</v>
       </c>
       <c r="C81" s="15" t="s">
-        <v>573</v>
+        <v>546</v>
       </c>
       <c r="D81" s="15" t="s">
-        <v>574</v>
+        <v>547</v>
       </c>
       <c r="E81" s="15" t="s">
-        <v>575</v>
+        <v>548</v>
       </c>
       <c r="F81" s="15" t="s">
-        <v>576</v>
+        <v>549</v>
       </c>
       <c r="G81" s="15" t="s">
-        <v>577</v>
+        <v>550</v>
       </c>
       <c r="H81" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I81" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I81" s="15"/>
     </row>
     <row r="82" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B82" s="15" t="s">
-        <v>578</v>
+        <v>551</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>579</v>
+        <v>552</v>
       </c>
       <c r="D82" s="15" t="s">
-        <v>580</v>
+        <v>553</v>
       </c>
       <c r="E82" s="15" t="s">
-        <v>581</v>
+        <v>554</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>582</v>
+        <v>555</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>583</v>
+        <v>556</v>
       </c>
       <c r="H82" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I82" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I82" s="15"/>
     </row>
     <row r="83" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B83" s="15" t="s">
-        <v>584</v>
+        <v>557</v>
       </c>
       <c r="C83" s="15" t="s">
-        <v>585</v>
+        <v>558</v>
       </c>
       <c r="D83" s="15" t="s">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="E83" s="15" t="s">
-        <v>587</v>
+        <v>560</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>588</v>
+        <v>561</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>589</v>
+        <v>562</v>
       </c>
       <c r="H83" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I83" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I83" s="15"/>
     </row>
     <row r="84" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B84" s="15" t="s">
-        <v>590</v>
+        <v>563</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>592</v>
+        <v>565</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>593</v>
+        <v>566</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>594</v>
+        <v>567</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>595</v>
+        <v>568</v>
       </c>
       <c r="H84" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I84" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I84" s="15"/>
     </row>
     <row r="85" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B85" s="15" t="s">
-        <v>596</v>
+        <v>569</v>
       </c>
       <c r="C85" s="15" t="s">
-        <v>597</v>
+        <v>570</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>598</v>
+        <v>571</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>599</v>
+        <v>572</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>600</v>
+        <v>573</v>
       </c>
       <c r="G85" s="15" t="s">
-        <v>601</v>
+        <v>574</v>
       </c>
       <c r="H85" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I85" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I85" s="15"/>
     </row>
     <row r="86" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B86" s="15" t="s">
-        <v>602</v>
+        <v>575</v>
       </c>
       <c r="C86" s="15" t="s">
-        <v>603</v>
+        <v>576</v>
       </c>
       <c r="D86" s="15" t="s">
-        <v>604</v>
+        <v>577</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>605</v>
+        <v>578</v>
       </c>
       <c r="F86" s="15" t="s">
-        <v>606</v>
+        <v>579</v>
       </c>
       <c r="G86" s="15" t="s">
-        <v>607</v>
+        <v>580</v>
       </c>
       <c r="H86" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I86" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I86" s="15"/>
     </row>
     <row r="87" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B87" s="15" t="s">
-        <v>608</v>
+        <v>581</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>609</v>
+        <v>582</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>610</v>
+        <v>583</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>611</v>
+        <v>584</v>
       </c>
       <c r="F87" s="15" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="G87" s="15" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="H87" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I87" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I87" s="15"/>
     </row>
     <row r="88" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>614</v>
+        <v>587</v>
       </c>
       <c r="C88" s="15" t="s">
-        <v>615</v>
+        <v>588</v>
       </c>
       <c r="D88" s="15" t="s">
-        <v>616</v>
+        <v>589</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>617</v>
+        <v>590</v>
       </c>
       <c r="F88" s="15" t="s">
-        <v>618</v>
+        <v>591</v>
       </c>
       <c r="G88" s="15" t="s">
-        <v>619</v>
+        <v>592</v>
       </c>
       <c r="H88" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I88" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I88" s="15"/>
     </row>
     <row r="89" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>621</v>
+        <v>594</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>622</v>
+        <v>595</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>623</v>
+        <v>596</v>
       </c>
       <c r="F89" s="15" t="s">
-        <v>624</v>
+        <v>597</v>
       </c>
       <c r="G89" s="15" t="s">
-        <v>625</v>
+        <v>598</v>
       </c>
       <c r="H89" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I89" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I89" s="15"/>
     </row>
     <row r="90" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B90" s="15" t="s">
-        <v>626</v>
+        <v>599</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>627</v>
+        <v>600</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>628</v>
+        <v>601</v>
       </c>
       <c r="E90" s="15" t="s">
-        <v>629</v>
+        <v>602</v>
       </c>
       <c r="F90" s="15" t="s">
-        <v>630</v>
+        <v>603</v>
       </c>
       <c r="G90" s="15" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="H90" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I90" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I90" s="15"/>
     </row>
     <row r="91" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>634</v>
+        <v>607</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>635</v>
+        <v>608</v>
       </c>
       <c r="F91" s="15" t="s">
-        <v>636</v>
+        <v>609</v>
       </c>
       <c r="G91" s="15" t="s">
-        <v>637</v>
+        <v>610</v>
       </c>
       <c r="H91" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I91" s="15" t="s">
-        <v>638</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I91" s="15"/>
     </row>
     <row r="92" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>639</v>
+        <v>611</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>640</v>
+        <v>612</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>641</v>
+        <v>613</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>642</v>
+        <v>614</v>
       </c>
       <c r="F92" s="15" t="s">
-        <v>643</v>
+        <v>615</v>
       </c>
       <c r="G92" s="15" t="s">
-        <v>644</v>
+        <v>616</v>
       </c>
       <c r="H92" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I92" s="15" t="s">
-        <v>645</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I92" s="15"/>
     </row>
     <row r="93" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B93" s="15" t="s">
-        <v>646</v>
+        <v>617</v>
       </c>
       <c r="C93" s="15" t="s">
-        <v>647</v>
+        <v>618</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>648</v>
+        <v>619</v>
       </c>
       <c r="E93" s="15" t="s">
-        <v>649</v>
+        <v>620</v>
       </c>
       <c r="F93" s="15" t="s">
-        <v>650</v>
+        <v>621</v>
       </c>
       <c r="G93" s="15" t="s">
-        <v>651</v>
+        <v>622</v>
       </c>
       <c r="H93" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I93" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I93" s="15"/>
     </row>
     <row r="94" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B94" s="15" t="s">
-        <v>652</v>
+        <v>623</v>
       </c>
       <c r="C94" s="15" t="s">
-        <v>653</v>
+        <v>624</v>
       </c>
       <c r="D94" s="15" t="s">
-        <v>654</v>
+        <v>625</v>
       </c>
       <c r="E94" s="15" t="s">
-        <v>655</v>
+        <v>626</v>
       </c>
       <c r="F94" s="15" t="s">
-        <v>656</v>
+        <v>627</v>
       </c>
       <c r="G94" s="15" t="s">
-        <v>657</v>
+        <v>628</v>
       </c>
       <c r="H94" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I94" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I94" s="15"/>
     </row>
     <row r="95" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>658</v>
+        <v>629</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>659</v>
+        <v>630</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>660</v>
+        <v>631</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>661</v>
+        <v>632</v>
       </c>
       <c r="F95" s="15" t="s">
-        <v>662</v>
+        <v>633</v>
       </c>
       <c r="G95" s="15" t="s">
-        <v>663</v>
+        <v>634</v>
       </c>
       <c r="H95" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I95" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I95" s="15"/>
     </row>
     <row r="96" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B96" s="15" t="s">
-        <v>664</v>
+        <v>635</v>
       </c>
       <c r="C96" s="15" t="s">
-        <v>665</v>
+        <v>636</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>666</v>
+        <v>637</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>667</v>
+        <v>638</v>
       </c>
       <c r="F96" s="15" t="s">
-        <v>668</v>
+        <v>639</v>
       </c>
       <c r="G96" s="15" t="s">
-        <v>669</v>
+        <v>640</v>
       </c>
       <c r="H96" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I96" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I96" s="15"/>
     </row>
     <row r="97" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B97" s="15" t="s">
-        <v>670</v>
+        <v>641</v>
       </c>
       <c r="C97" s="15" t="s">
-        <v>671</v>
+        <v>642</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>672</v>
+        <v>643</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>673</v>
+        <v>644</v>
       </c>
       <c r="F97" s="15" t="s">
-        <v>674</v>
+        <v>645</v>
       </c>
       <c r="G97" s="15" t="s">
-        <v>675</v>
+        <v>646</v>
       </c>
       <c r="H97" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I97" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I97" s="15"/>
     </row>
     <row r="98" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>676</v>
+        <v>647</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>677</v>
+        <v>648</v>
       </c>
       <c r="D98" s="15" t="s">
-        <v>678</v>
+        <v>649</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>679</v>
+        <v>650</v>
       </c>
       <c r="F98" s="15" t="s">
-        <v>680</v>
+        <v>651</v>
       </c>
       <c r="G98" s="15" t="s">
-        <v>681</v>
+        <v>652</v>
       </c>
       <c r="H98" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I98" s="15" t="s">
-        <v>682</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I98" s="15"/>
     </row>
     <row r="99" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>683</v>
+        <v>653</v>
       </c>
       <c r="C99" s="15" t="s">
-        <v>684</v>
+        <v>654</v>
       </c>
       <c r="D99" s="15" t="s">
-        <v>685</v>
+        <v>655</v>
       </c>
       <c r="E99" s="15" t="s">
-        <v>686</v>
+        <v>656</v>
       </c>
       <c r="F99" s="15" t="s">
-        <v>687</v>
+        <v>657</v>
       </c>
       <c r="G99" s="15" t="s">
-        <v>688</v>
+        <v>658</v>
       </c>
       <c r="H99" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I99" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I99" s="15"/>
     </row>
     <row r="100" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>689</v>
+        <v>659</v>
       </c>
       <c r="C100" s="15" t="s">
-        <v>690</v>
+        <v>660</v>
       </c>
       <c r="D100" s="15" t="s">
-        <v>691</v>
+        <v>661</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>692</v>
+        <v>662</v>
       </c>
       <c r="F100" s="15" t="s">
-        <v>693</v>
+        <v>663</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>694</v>
+        <v>664</v>
       </c>
       <c r="H100" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I100" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I100" s="15"/>
     </row>
     <row r="101" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>695</v>
+        <v>665</v>
       </c>
       <c r="C101" s="15" t="s">
-        <v>696</v>
+        <v>666</v>
       </c>
       <c r="D101" s="15" t="s">
-        <v>697</v>
+        <v>667</v>
       </c>
       <c r="E101" s="15" t="s">
-        <v>698</v>
+        <v>668</v>
       </c>
       <c r="F101" s="15" t="s">
-        <v>699</v>
+        <v>669</v>
       </c>
       <c r="G101" s="15" t="s">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="H101" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I101" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I101" s="15"/>
     </row>
     <row r="102" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>701</v>
+        <v>671</v>
       </c>
       <c r="C102" s="15" t="s">
-        <v>702</v>
+        <v>672</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>703</v>
+        <v>673</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>704</v>
+        <v>674</v>
       </c>
       <c r="F102" s="15" t="s">
-        <v>705</v>
+        <v>675</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>706</v>
+        <v>676</v>
       </c>
       <c r="H102" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I102" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I102" s="15"/>
     </row>
     <row r="103" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>707</v>
+        <v>677</v>
       </c>
       <c r="C103" s="15" t="s">
-        <v>708</v>
+        <v>678</v>
       </c>
       <c r="D103" s="15" t="s">
-        <v>709</v>
+        <v>679</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>710</v>
+        <v>680</v>
       </c>
       <c r="F103" s="15" t="s">
-        <v>711</v>
+        <v>681</v>
       </c>
       <c r="G103" s="15" t="s">
-        <v>712</v>
+        <v>682</v>
       </c>
       <c r="H103" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I103" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I103" s="15"/>
     </row>
     <row r="104" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>713</v>
+        <v>683</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>714</v>
+        <v>684</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>715</v>
+        <v>685</v>
       </c>
       <c r="E104" s="15" t="s">
-        <v>716</v>
+        <v>686</v>
       </c>
       <c r="F104" s="15" t="s">
-        <v>717</v>
+        <v>687</v>
       </c>
       <c r="G104" s="15" t="s">
-        <v>718</v>
+        <v>688</v>
       </c>
       <c r="H104" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I104" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I104" s="15"/>
     </row>
     <row r="105" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>719</v>
+        <v>689</v>
       </c>
       <c r="C105" s="15" t="s">
-        <v>720</v>
+        <v>690</v>
       </c>
       <c r="D105" s="15" t="s">
-        <v>721</v>
+        <v>691</v>
       </c>
       <c r="E105" s="15" t="s">
-        <v>722</v>
+        <v>692</v>
       </c>
       <c r="F105" s="15" t="s">
-        <v>723</v>
+        <v>693</v>
       </c>
       <c r="G105" s="15" t="s">
-        <v>724</v>
+        <v>694</v>
       </c>
       <c r="H105" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I105" s="15" t="s">
-        <v>725</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I105" s="15"/>
     </row>
     <row r="106" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>726</v>
+        <v>695</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>727</v>
+        <v>696</v>
       </c>
       <c r="D106" s="15" t="s">
-        <v>728</v>
+        <v>697</v>
       </c>
       <c r="E106" s="15" t="s">
-        <v>729</v>
+        <v>698</v>
       </c>
       <c r="F106" s="15" t="s">
-        <v>730</v>
+        <v>699</v>
       </c>
       <c r="G106" s="15" t="s">
-        <v>731</v>
+        <v>700</v>
       </c>
       <c r="H106" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I106" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I106" s="15"/>
     </row>
     <row r="107" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="C107" s="15" t="s">
-        <v>733</v>
+        <v>702</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>734</v>
+        <v>703</v>
       </c>
       <c r="E107" s="15" t="s">
-        <v>735</v>
+        <v>704</v>
       </c>
       <c r="F107" s="15" t="s">
-        <v>736</v>
+        <v>705</v>
       </c>
       <c r="G107" s="15" t="s">
-        <v>737</v>
+        <v>706</v>
       </c>
       <c r="H107" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I107" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I107" s="15"/>
     </row>
     <row r="108" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>738</v>
+        <v>707</v>
       </c>
       <c r="C108" s="15" t="s">
-        <v>739</v>
+        <v>708</v>
       </c>
       <c r="D108" s="15" t="s">
-        <v>740</v>
+        <v>709</v>
       </c>
       <c r="E108" s="15" t="s">
-        <v>741</v>
+        <v>710</v>
       </c>
       <c r="F108" s="15" t="s">
-        <v>742</v>
+        <v>711</v>
       </c>
       <c r="G108" s="15" t="s">
-        <v>743</v>
+        <v>712</v>
       </c>
       <c r="H108" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I108" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I108" s="15"/>
     </row>
     <row r="109" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="C109" s="15" t="s">
-        <v>745</v>
+        <v>714</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="E109" s="15" t="s">
-        <v>747</v>
+        <v>716</v>
       </c>
       <c r="F109" s="15" t="s">
-        <v>748</v>
+        <v>717</v>
       </c>
       <c r="G109" s="15" t="s">
-        <v>749</v>
+        <v>718</v>
       </c>
       <c r="H109" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I109" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I109" s="15"/>
     </row>
     <row r="110" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>750</v>
+        <v>719</v>
       </c>
       <c r="C110" s="15" t="s">
-        <v>751</v>
+        <v>720</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>752</v>
+        <v>721</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>753</v>
+        <v>722</v>
       </c>
       <c r="F110" s="15" t="s">
-        <v>754</v>
+        <v>723</v>
       </c>
       <c r="G110" s="15" t="s">
-        <v>755</v>
+        <v>724</v>
       </c>
       <c r="H110" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I110" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I110" s="15"/>
     </row>
     <row r="111" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>756</v>
+        <v>725</v>
       </c>
       <c r="C111" s="15" t="s">
-        <v>757</v>
+        <v>726</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>758</v>
+        <v>727</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>759</v>
+        <v>728</v>
       </c>
       <c r="F111" s="15" t="s">
-        <v>760</v>
+        <v>729</v>
       </c>
       <c r="G111" s="15" t="s">
-        <v>761</v>
+        <v>730</v>
       </c>
       <c r="H111" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I111" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I111" s="15"/>
     </row>
     <row r="112" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>762</v>
+        <v>731</v>
       </c>
       <c r="C112" s="15" t="s">
-        <v>763</v>
+        <v>732</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>764</v>
+        <v>733</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>765</v>
+        <v>734</v>
       </c>
       <c r="F112" s="15" t="s">
-        <v>766</v>
+        <v>735</v>
       </c>
       <c r="G112" s="15" t="s">
-        <v>767</v>
+        <v>736</v>
       </c>
       <c r="H112" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I112" s="15" t="s">
-        <v>768</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I112" s="15"/>
     </row>
     <row r="113" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>769</v>
+        <v>737</v>
       </c>
       <c r="C113" s="15" t="s">
-        <v>770</v>
+        <v>738</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>771</v>
+        <v>739</v>
       </c>
       <c r="E113" s="15" t="s">
-        <v>772</v>
+        <v>740</v>
       </c>
       <c r="F113" s="15" t="s">
-        <v>773</v>
+        <v>741</v>
       </c>
       <c r="G113" s="15" t="s">
-        <v>774</v>
+        <v>742</v>
       </c>
       <c r="H113" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I113" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I113" s="15"/>
     </row>
     <row r="114" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>775</v>
+        <v>743</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>776</v>
+        <v>744</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>777</v>
+        <v>745</v>
       </c>
       <c r="E114" s="15" t="s">
-        <v>778</v>
+        <v>746</v>
       </c>
       <c r="F114" s="15" t="s">
-        <v>779</v>
+        <v>747</v>
       </c>
       <c r="G114" s="15" t="s">
-        <v>780</v>
+        <v>748</v>
       </c>
       <c r="H114" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I114" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I114" s="15"/>
     </row>
     <row r="115" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>781</v>
+        <v>749</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>782</v>
+        <v>750</v>
       </c>
       <c r="D115" s="15" t="s">
-        <v>783</v>
+        <v>751</v>
       </c>
       <c r="E115" s="15" t="s">
-        <v>784</v>
+        <v>752</v>
       </c>
       <c r="F115" s="15" t="s">
-        <v>785</v>
+        <v>753</v>
       </c>
       <c r="G115" s="15" t="s">
-        <v>786</v>
+        <v>754</v>
       </c>
       <c r="H115" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I115" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I115" s="15"/>
     </row>
     <row r="116" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>787</v>
+        <v>755</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>788</v>
+        <v>756</v>
       </c>
       <c r="D116" s="15" t="s">
-        <v>789</v>
+        <v>757</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>790</v>
+        <v>758</v>
       </c>
       <c r="F116" s="15" t="s">
-        <v>791</v>
+        <v>759</v>
       </c>
       <c r="G116" s="15" t="s">
-        <v>792</v>
+        <v>760</v>
       </c>
       <c r="H116" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I116" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I116" s="15"/>
     </row>
     <row r="117" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>793</v>
+        <v>761</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>794</v>
+        <v>762</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>795</v>
+        <v>763</v>
       </c>
       <c r="E117" s="15" t="s">
-        <v>796</v>
+        <v>764</v>
       </c>
       <c r="F117" s="15" t="s">
-        <v>797</v>
+        <v>765</v>
       </c>
       <c r="G117" s="15" t="s">
-        <v>798</v>
+        <v>766</v>
       </c>
       <c r="H117" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I117" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I117" s="15"/>
     </row>
     <row r="118" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>799</v>
+        <v>767</v>
       </c>
       <c r="C118" s="15" t="s">
-        <v>800</v>
+        <v>768</v>
       </c>
       <c r="D118" s="15" t="s">
-        <v>801</v>
+        <v>769</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>802</v>
+        <v>770</v>
       </c>
       <c r="F118" s="15" t="s">
-        <v>803</v>
+        <v>771</v>
       </c>
       <c r="G118" s="15" t="s">
-        <v>804</v>
+        <v>772</v>
       </c>
       <c r="H118" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I118" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I118" s="15"/>
     </row>
     <row r="119" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>805</v>
+        <v>773</v>
       </c>
       <c r="C119" s="15" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="D119" s="15" t="s">
-        <v>807</v>
+        <v>775</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>808</v>
+        <v>776</v>
       </c>
       <c r="F119" s="15" t="s">
-        <v>809</v>
+        <v>777</v>
       </c>
       <c r="G119" s="15" t="s">
-        <v>810</v>
+        <v>778</v>
       </c>
       <c r="H119" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I119" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I119" s="15"/>
     </row>
     <row r="120" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>811</v>
+        <v>779</v>
       </c>
       <c r="C120" s="15" t="s">
-        <v>812</v>
+        <v>780</v>
       </c>
       <c r="D120" s="15" t="s">
-        <v>813</v>
+        <v>781</v>
       </c>
       <c r="E120" s="15" t="s">
-        <v>814</v>
+        <v>782</v>
       </c>
       <c r="F120" s="15" t="s">
-        <v>815</v>
+        <v>783</v>
       </c>
       <c r="G120" s="15" t="s">
-        <v>816</v>
+        <v>784</v>
       </c>
       <c r="H120" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I120" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I120" s="15"/>
     </row>
     <row r="121" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>817</v>
+        <v>785</v>
       </c>
       <c r="C121" s="15" t="s">
-        <v>818</v>
+        <v>786</v>
       </c>
       <c r="D121" s="15" t="s">
-        <v>819</v>
+        <v>787</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>820</v>
+        <v>788</v>
       </c>
       <c r="F121" s="15" t="s">
-        <v>821</v>
+        <v>789</v>
       </c>
       <c r="G121" s="15" t="s">
-        <v>822</v>
+        <v>790</v>
       </c>
       <c r="H121" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I121" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I121" s="15"/>
     </row>
     <row r="122" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>823</v>
+        <v>791</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>824</v>
+        <v>792</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>825</v>
+        <v>793</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>826</v>
+        <v>794</v>
       </c>
       <c r="F122" s="15" t="s">
-        <v>827</v>
+        <v>795</v>
       </c>
       <c r="G122" s="15" t="s">
-        <v>828</v>
+        <v>796</v>
       </c>
       <c r="H122" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I122" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I122" s="15"/>
     </row>
     <row r="123" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>829</v>
+        <v>797</v>
       </c>
       <c r="C123" s="15" t="s">
-        <v>830</v>
+        <v>798</v>
       </c>
       <c r="D123" s="15" t="s">
-        <v>831</v>
+        <v>799</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>832</v>
+        <v>800</v>
       </c>
       <c r="F123" s="15" t="s">
-        <v>833</v>
+        <v>801</v>
       </c>
       <c r="G123" s="15" t="s">
-        <v>834</v>
+        <v>802</v>
       </c>
       <c r="H123" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I123" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I123" s="15"/>
     </row>
     <row r="124" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>835</v>
+        <v>803</v>
       </c>
       <c r="C124" s="15" t="s">
-        <v>836</v>
+        <v>804</v>
       </c>
       <c r="D124" s="15" t="s">
-        <v>837</v>
+        <v>805</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>838</v>
+        <v>806</v>
       </c>
       <c r="F124" s="15" t="s">
-        <v>839</v>
+        <v>807</v>
       </c>
       <c r="G124" s="15" t="s">
-        <v>840</v>
+        <v>808</v>
       </c>
       <c r="H124" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I124" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I124" s="15"/>
     </row>
     <row r="125" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>841</v>
+        <v>809</v>
       </c>
       <c r="C125" s="15" t="s">
-        <v>842</v>
+        <v>810</v>
       </c>
       <c r="D125" s="15" t="s">
-        <v>843</v>
+        <v>811</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>844</v>
+        <v>812</v>
       </c>
       <c r="F125" s="15" t="s">
-        <v>845</v>
+        <v>813</v>
       </c>
       <c r="G125" s="15" t="s">
-        <v>846</v>
+        <v>814</v>
       </c>
       <c r="H125" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I125" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I125" s="15"/>
     </row>
     <row r="126" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>847</v>
+        <v>815</v>
       </c>
       <c r="C126" s="15" t="s">
-        <v>848</v>
+        <v>816</v>
       </c>
       <c r="D126" s="15" t="s">
-        <v>849</v>
+        <v>817</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>850</v>
+        <v>818</v>
       </c>
       <c r="F126" s="15" t="s">
-        <v>851</v>
+        <v>819</v>
       </c>
       <c r="G126" s="15" t="s">
-        <v>852</v>
+        <v>820</v>
       </c>
       <c r="H126" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I126" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I126" s="15"/>
     </row>
     <row r="127" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>853</v>
+        <v>821</v>
       </c>
       <c r="C127" s="15" t="s">
-        <v>854</v>
+        <v>822</v>
       </c>
       <c r="D127" s="15" t="s">
-        <v>855</v>
+        <v>823</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>856</v>
+        <v>824</v>
       </c>
       <c r="F127" s="15" t="s">
-        <v>857</v>
+        <v>825</v>
       </c>
       <c r="G127" s="15" t="s">
-        <v>858</v>
+        <v>826</v>
       </c>
       <c r="H127" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I127" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I127" s="15"/>
     </row>
     <row r="128" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>859</v>
+        <v>827</v>
       </c>
       <c r="C128" s="15" t="s">
-        <v>860</v>
+        <v>828</v>
       </c>
       <c r="D128" s="15" t="s">
-        <v>861</v>
+        <v>829</v>
       </c>
       <c r="E128" s="15" t="s">
-        <v>862</v>
+        <v>830</v>
       </c>
       <c r="F128" s="15" t="s">
-        <v>863</v>
+        <v>831</v>
       </c>
       <c r="G128" s="15" t="s">
-        <v>864</v>
+        <v>832</v>
       </c>
       <c r="H128" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I128" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I128" s="15"/>
     </row>
     <row r="129" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>865</v>
+        <v>833</v>
       </c>
       <c r="C129" s="15" t="s">
-        <v>866</v>
+        <v>834</v>
       </c>
       <c r="D129" s="15" t="s">
-        <v>867</v>
+        <v>835</v>
       </c>
       <c r="E129" s="15" t="s">
-        <v>868</v>
+        <v>836</v>
       </c>
       <c r="F129" s="15" t="s">
-        <v>869</v>
+        <v>837</v>
       </c>
       <c r="G129" s="15" t="s">
-        <v>870</v>
+        <v>838</v>
       </c>
       <c r="H129" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I129" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I129" s="15"/>
     </row>
     <row r="130" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>871</v>
+        <v>839</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>872</v>
+        <v>840</v>
       </c>
       <c r="D130" s="15" t="s">
-        <v>873</v>
+        <v>841</v>
       </c>
       <c r="E130" s="15" t="s">
-        <v>874</v>
+        <v>842</v>
       </c>
       <c r="F130" s="15" t="s">
-        <v>875</v>
+        <v>843</v>
       </c>
       <c r="G130" s="15" t="s">
-        <v>876</v>
+        <v>844</v>
       </c>
       <c r="H130" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I130" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I130" s="15"/>
     </row>
     <row r="131" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>877</v>
+        <v>845</v>
       </c>
       <c r="C131" s="15" t="s">
-        <v>878</v>
+        <v>846</v>
       </c>
       <c r="D131" s="15" t="s">
-        <v>879</v>
+        <v>847</v>
       </c>
       <c r="E131" s="15" t="s">
-        <v>880</v>
+        <v>848</v>
       </c>
       <c r="F131" s="15" t="s">
-        <v>881</v>
+        <v>849</v>
       </c>
       <c r="G131" s="15" t="s">
-        <v>882</v>
+        <v>850</v>
       </c>
       <c r="H131" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I131" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I131" s="15"/>
     </row>
     <row r="132" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>883</v>
+        <v>851</v>
       </c>
       <c r="C132" s="15" t="s">
-        <v>884</v>
+        <v>852</v>
       </c>
       <c r="D132" s="15" t="s">
-        <v>885</v>
+        <v>853</v>
       </c>
       <c r="E132" s="15" t="s">
-        <v>886</v>
+        <v>854</v>
       </c>
       <c r="F132" s="15" t="s">
-        <v>887</v>
+        <v>855</v>
       </c>
       <c r="G132" s="15" t="s">
-        <v>888</v>
+        <v>856</v>
       </c>
       <c r="H132" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I132" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I132" s="15"/>
     </row>
     <row r="133" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>889</v>
+        <v>857</v>
       </c>
       <c r="C133" s="15" t="s">
-        <v>890</v>
+        <v>858</v>
       </c>
       <c r="D133" s="15" t="s">
-        <v>891</v>
+        <v>859</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>892</v>
+        <v>860</v>
       </c>
       <c r="F133" s="15" t="s">
-        <v>893</v>
+        <v>861</v>
       </c>
       <c r="G133" s="15" t="s">
-        <v>894</v>
+        <v>862</v>
       </c>
       <c r="H133" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I133" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I133" s="15"/>
     </row>
     <row r="134" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>895</v>
+        <v>863</v>
       </c>
       <c r="C134" s="15" t="s">
-        <v>896</v>
+        <v>864</v>
       </c>
       <c r="D134" s="15" t="s">
-        <v>897</v>
+        <v>865</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>898</v>
+        <v>866</v>
       </c>
       <c r="F134" s="15" t="s">
-        <v>899</v>
+        <v>867</v>
       </c>
       <c r="G134" s="15" t="s">
-        <v>900</v>
+        <v>868</v>
       </c>
       <c r="H134" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I134" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I134" s="15"/>
     </row>
     <row r="135" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>901</v>
+        <v>869</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>902</v>
+        <v>870</v>
       </c>
       <c r="D135" s="15" t="s">
-        <v>903</v>
+        <v>871</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>904</v>
+        <v>872</v>
       </c>
       <c r="F135" s="15" t="s">
-        <v>905</v>
+        <v>873</v>
       </c>
       <c r="G135" s="15" t="s">
-        <v>906</v>
+        <v>874</v>
       </c>
       <c r="H135" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I135" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I135" s="15"/>
     </row>
     <row r="136" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>907</v>
+        <v>875</v>
       </c>
       <c r="C136" s="15" t="s">
-        <v>908</v>
+        <v>876</v>
       </c>
       <c r="D136" s="15" t="s">
-        <v>909</v>
+        <v>877</v>
       </c>
       <c r="E136" s="15" t="s">
-        <v>910</v>
+        <v>878</v>
       </c>
       <c r="F136" s="15" t="s">
-        <v>911</v>
+        <v>879</v>
       </c>
       <c r="G136" s="15" t="s">
-        <v>912</v>
+        <v>880</v>
       </c>
       <c r="H136" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I136" s="15" t="s">
-        <v>913</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I136" s="15"/>
     </row>
     <row r="137" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>914</v>
+        <v>881</v>
       </c>
       <c r="C137" s="15" t="s">
-        <v>915</v>
+        <v>882</v>
       </c>
       <c r="D137" s="15" t="s">
-        <v>916</v>
+        <v>883</v>
       </c>
       <c r="E137" s="15" t="s">
-        <v>917</v>
+        <v>884</v>
       </c>
       <c r="F137" s="15" t="s">
-        <v>918</v>
+        <v>885</v>
       </c>
       <c r="G137" s="15" t="s">
-        <v>919</v>
+        <v>886</v>
       </c>
       <c r="H137" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I137" s="15" t="s">
-        <v>920</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I137" s="15"/>
     </row>
     <row r="138" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>921</v>
+        <v>887</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>922</v>
+        <v>888</v>
       </c>
       <c r="D138" s="15" t="s">
-        <v>923</v>
+        <v>889</v>
       </c>
       <c r="E138" s="15" t="s">
-        <v>924</v>
+        <v>890</v>
       </c>
       <c r="F138" s="15" t="s">
-        <v>925</v>
+        <v>891</v>
       </c>
       <c r="G138" s="15" t="s">
-        <v>926</v>
+        <v>892</v>
       </c>
       <c r="H138" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I138" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I138" s="15"/>
     </row>
     <row r="139" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>927</v>
+        <v>893</v>
       </c>
       <c r="C139" s="15" t="s">
-        <v>928</v>
+        <v>894</v>
       </c>
       <c r="D139" s="15" t="s">
-        <v>929</v>
+        <v>895</v>
       </c>
       <c r="E139" s="15" t="s">
-        <v>930</v>
+        <v>896</v>
       </c>
       <c r="F139" s="15" t="s">
-        <v>931</v>
+        <v>897</v>
       </c>
       <c r="G139" s="15" t="s">
-        <v>932</v>
+        <v>898</v>
       </c>
       <c r="H139" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I139" s="15" t="s">
-        <v>933</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I139" s="15"/>
     </row>
     <row r="140" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B140" s="15" t="s">
-        <v>934</v>
+        <v>899</v>
       </c>
       <c r="C140" s="15" t="s">
-        <v>935</v>
+        <v>900</v>
       </c>
       <c r="D140" s="15" t="s">
-        <v>936</v>
+        <v>901</v>
       </c>
       <c r="E140" s="15" t="s">
-        <v>937</v>
+        <v>902</v>
       </c>
       <c r="F140" s="15" t="s">
-        <v>938</v>
+        <v>903</v>
       </c>
       <c r="G140" s="15" t="s">
-        <v>939</v>
+        <v>904</v>
       </c>
       <c r="H140" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I140" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I140" s="15"/>
     </row>
     <row r="141" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>940</v>
+        <v>905</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>941</v>
+        <v>906</v>
       </c>
       <c r="D141" s="15" t="s">
-        <v>942</v>
+        <v>907</v>
       </c>
       <c r="E141" s="15" t="s">
-        <v>943</v>
+        <v>908</v>
       </c>
       <c r="F141" s="15" t="s">
-        <v>944</v>
+        <v>909</v>
       </c>
       <c r="G141" s="15" t="s">
-        <v>945</v>
+        <v>910</v>
       </c>
       <c r="H141" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I141" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I141" s="15"/>
     </row>
     <row r="142" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B142" s="15" t="s">
-        <v>946</v>
+        <v>911</v>
       </c>
       <c r="C142" s="15" t="s">
-        <v>947</v>
+        <v>912</v>
       </c>
       <c r="D142" s="15" t="s">
-        <v>948</v>
+        <v>913</v>
       </c>
       <c r="E142" s="15" t="s">
-        <v>949</v>
+        <v>914</v>
       </c>
       <c r="F142" s="15" t="s">
-        <v>950</v>
+        <v>915</v>
       </c>
       <c r="G142" s="15" t="s">
-        <v>951</v>
+        <v>916</v>
       </c>
       <c r="H142" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I142" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I142" s="15"/>
     </row>
     <row r="143" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B143" s="15" t="s">
-        <v>952</v>
+        <v>917</v>
       </c>
       <c r="C143" s="15" t="s">
-        <v>953</v>
+        <v>918</v>
       </c>
       <c r="D143" s="15" t="s">
-        <v>954</v>
+        <v>919</v>
       </c>
       <c r="E143" s="15" t="s">
-        <v>955</v>
+        <v>920</v>
       </c>
       <c r="F143" s="15" t="s">
-        <v>956</v>
+        <v>921</v>
       </c>
       <c r="G143" s="15" t="s">
-        <v>957</v>
+        <v>922</v>
       </c>
       <c r="H143" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I143" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I143" s="15"/>
     </row>
     <row r="144" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B144" s="15" t="s">
-        <v>958</v>
+        <v>923</v>
       </c>
       <c r="C144" s="15" t="s">
-        <v>959</v>
+        <v>924</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>960</v>
+        <v>925</v>
       </c>
       <c r="E144" s="15" t="s">
-        <v>961</v>
+        <v>926</v>
       </c>
       <c r="F144" s="15" t="s">
-        <v>962</v>
+        <v>927</v>
       </c>
       <c r="G144" s="15" t="s">
-        <v>963</v>
+        <v>928</v>
       </c>
       <c r="H144" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I144" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I144" s="15"/>
     </row>
     <row r="145" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B145" s="15" t="s">
-        <v>964</v>
+        <v>929</v>
       </c>
       <c r="C145" s="15" t="s">
-        <v>965</v>
+        <v>930</v>
       </c>
       <c r="D145" s="15" t="s">
-        <v>966</v>
+        <v>931</v>
       </c>
       <c r="E145" s="15" t="s">
-        <v>967</v>
+        <v>932</v>
       </c>
       <c r="F145" s="15" t="s">
-        <v>968</v>
+        <v>933</v>
       </c>
       <c r="G145" s="15" t="s">
-        <v>969</v>
+        <v>934</v>
       </c>
       <c r="H145" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I145" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I145" s="15"/>
     </row>
     <row r="146" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B146" s="15" t="s">
-        <v>970</v>
+        <v>935</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>971</v>
+        <v>936</v>
       </c>
       <c r="D146" s="15" t="s">
-        <v>972</v>
+        <v>937</v>
       </c>
       <c r="E146" s="15" t="s">
-        <v>973</v>
+        <v>938</v>
       </c>
       <c r="F146" s="15" t="s">
-        <v>974</v>
+        <v>939</v>
       </c>
       <c r="G146" s="15" t="s">
-        <v>975</v>
+        <v>940</v>
       </c>
       <c r="H146" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I146" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I146" s="15"/>
     </row>
     <row r="147" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B147" s="15" t="s">
-        <v>976</v>
+        <v>941</v>
       </c>
       <c r="C147" s="15" t="s">
-        <v>977</v>
+        <v>942</v>
       </c>
       <c r="D147" s="15" t="s">
-        <v>978</v>
+        <v>943</v>
       </c>
       <c r="E147" s="15" t="s">
-        <v>979</v>
+        <v>944</v>
       </c>
       <c r="F147" s="15" t="s">
-        <v>980</v>
+        <v>945</v>
       </c>
       <c r="G147" s="15" t="s">
-        <v>981</v>
+        <v>946</v>
       </c>
       <c r="H147" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I147" s="15" t="s">
-        <v>982</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I147" s="15"/>
     </row>
     <row r="148" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B148" s="15" t="s">
-        <v>983</v>
+        <v>947</v>
       </c>
       <c r="C148" s="15" t="s">
-        <v>984</v>
+        <v>948</v>
       </c>
       <c r="D148" s="15" t="s">
-        <v>985</v>
+        <v>949</v>
       </c>
       <c r="E148" s="15" t="s">
-        <v>986</v>
+        <v>950</v>
       </c>
       <c r="F148" s="15" t="s">
-        <v>987</v>
+        <v>951</v>
       </c>
       <c r="G148" s="15" t="s">
-        <v>988</v>
+        <v>952</v>
       </c>
       <c r="H148" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I148" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I148" s="15"/>
     </row>
     <row r="149" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B149" s="15" t="s">
-        <v>989</v>
+        <v>953</v>
       </c>
       <c r="C149" s="15" t="s">
-        <v>990</v>
+        <v>954</v>
       </c>
       <c r="D149" s="15" t="s">
-        <v>991</v>
+        <v>955</v>
       </c>
       <c r="E149" s="15" t="s">
-        <v>992</v>
+        <v>956</v>
       </c>
       <c r="F149" s="15" t="s">
-        <v>993</v>
+        <v>957</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>994</v>
+        <v>958</v>
       </c>
       <c r="H149" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I149" s="15" t="s">
-        <v>995</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I149" s="15"/>
     </row>
     <row r="150" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B150" s="15" t="s">
-        <v>996</v>
+        <v>959</v>
       </c>
       <c r="C150" s="15" t="s">
-        <v>997</v>
+        <v>960</v>
       </c>
       <c r="D150" s="15" t="s">
-        <v>998</v>
+        <v>961</v>
       </c>
       <c r="E150" s="15" t="s">
-        <v>999</v>
+        <v>962</v>
       </c>
       <c r="F150" s="15" t="s">
-        <v>1000</v>
+        <v>963</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>1001</v>
+        <v>964</v>
       </c>
       <c r="H150" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I150" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I150" s="15"/>
     </row>
     <row r="151" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B151" s="15" t="s">
-        <v>1002</v>
+        <v>965</v>
       </c>
       <c r="C151" s="15" t="s">
-        <v>1003</v>
+        <v>966</v>
       </c>
       <c r="D151" s="15" t="s">
-        <v>1004</v>
+        <v>967</v>
       </c>
       <c r="E151" s="15" t="s">
-        <v>1005</v>
+        <v>968</v>
       </c>
       <c r="F151" s="15" t="s">
-        <v>1006</v>
+        <v>969</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>1007</v>
+        <v>970</v>
       </c>
       <c r="H151" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I151" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I151" s="15"/>
     </row>
     <row r="152" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B152" s="15" t="s">
-        <v>1008</v>
+        <v>971</v>
       </c>
       <c r="C152" s="15" t="s">
-        <v>1009</v>
+        <v>972</v>
       </c>
       <c r="D152" s="15" t="s">
-        <v>1010</v>
+        <v>973</v>
       </c>
       <c r="E152" s="15" t="s">
-        <v>1011</v>
+        <v>974</v>
       </c>
       <c r="F152" s="15" t="s">
-        <v>1012</v>
+        <v>975</v>
       </c>
       <c r="G152" s="15" t="s">
-        <v>1013</v>
+        <v>976</v>
       </c>
       <c r="H152" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I152" s="15" t="s">
-        <v>1014</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I152" s="15"/>
     </row>
     <row r="153" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B153" s="15" t="s">
-        <v>1015</v>
+        <v>977</v>
       </c>
       <c r="C153" s="15" t="s">
-        <v>1016</v>
+        <v>978</v>
       </c>
       <c r="D153" s="15" t="s">
-        <v>1017</v>
+        <v>979</v>
       </c>
       <c r="E153" s="15" t="s">
-        <v>1018</v>
+        <v>980</v>
       </c>
       <c r="F153" s="15" t="s">
-        <v>1019</v>
+        <v>981</v>
       </c>
       <c r="G153" s="15" t="s">
-        <v>1020</v>
+        <v>982</v>
       </c>
       <c r="H153" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I153" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I153" s="15"/>
     </row>
     <row r="154" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B154" s="15" t="s">
-        <v>1021</v>
+        <v>983</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>1022</v>
+        <v>984</v>
       </c>
       <c r="D154" s="15" t="s">
-        <v>1023</v>
+        <v>985</v>
       </c>
       <c r="E154" s="15" t="s">
-        <v>1024</v>
+        <v>986</v>
       </c>
       <c r="F154" s="15" t="s">
-        <v>1025</v>
+        <v>987</v>
       </c>
       <c r="G154" s="15" t="s">
-        <v>1026</v>
+        <v>988</v>
       </c>
       <c r="H154" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I154" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I154" s="15"/>
     </row>
     <row r="155" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>1027</v>
+        <v>989</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>1028</v>
+        <v>990</v>
       </c>
       <c r="D155" s="15" t="s">
-        <v>1029</v>
+        <v>991</v>
       </c>
       <c r="E155" s="15" t="s">
-        <v>1030</v>
+        <v>992</v>
       </c>
       <c r="F155" s="15" t="s">
-        <v>1031</v>
+        <v>993</v>
       </c>
       <c r="G155" s="15" t="s">
-        <v>1032</v>
+        <v>994</v>
       </c>
       <c r="H155" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I155" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I155" s="15"/>
     </row>
     <row r="156" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>1033</v>
+        <v>995</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>1034</v>
+        <v>996</v>
       </c>
       <c r="D156" s="15" t="s">
-        <v>1035</v>
+        <v>997</v>
       </c>
       <c r="E156" s="15" t="s">
-        <v>1036</v>
+        <v>998</v>
       </c>
       <c r="F156" s="15" t="s">
-        <v>1037</v>
+        <v>999</v>
       </c>
       <c r="G156" s="15" t="s">
-        <v>1038</v>
+        <v>1000</v>
       </c>
       <c r="H156" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I156" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I156" s="15"/>
     </row>
     <row r="157" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>1039</v>
+        <v>1001</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>1040</v>
+        <v>1002</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>1041</v>
+        <v>1003</v>
       </c>
       <c r="E157" s="15" t="s">
-        <v>1042</v>
+        <v>1004</v>
       </c>
       <c r="F157" s="15" t="s">
-        <v>1043</v>
+        <v>1005</v>
       </c>
       <c r="G157" s="15" t="s">
-        <v>1044</v>
+        <v>1006</v>
       </c>
       <c r="H157" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I157" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I157" s="15"/>
     </row>
     <row r="158" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>1045</v>
+        <v>1007</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>1046</v>
+        <v>1008</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>1047</v>
+        <v>1009</v>
       </c>
       <c r="E158" s="15" t="s">
-        <v>1048</v>
+        <v>1010</v>
       </c>
       <c r="F158" s="15" t="s">
-        <v>1049</v>
+        <v>1011</v>
       </c>
       <c r="G158" s="15" t="s">
-        <v>1050</v>
+        <v>1012</v>
       </c>
       <c r="H158" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I158" s="15" t="s">
-        <v>1051</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I158" s="15"/>
     </row>
     <row r="159" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B159" s="15" t="s">
-        <v>1052</v>
+        <v>1013</v>
       </c>
       <c r="C159" s="15" t="s">
-        <v>1053</v>
+        <v>1014</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>1054</v>
+        <v>1015</v>
       </c>
       <c r="E159" s="15" t="s">
-        <v>1055</v>
+        <v>1016</v>
       </c>
       <c r="F159" s="15" t="s">
-        <v>1056</v>
+        <v>1017</v>
       </c>
       <c r="G159" s="15" t="s">
-        <v>1057</v>
+        <v>1018</v>
       </c>
       <c r="H159" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I159" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I159" s="15"/>
     </row>
     <row r="160" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B160" s="15" t="s">
-        <v>1058</v>
+        <v>1019</v>
       </c>
       <c r="C160" s="15" t="s">
-        <v>1059</v>
+        <v>1020</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>1060</v>
+        <v>1021</v>
       </c>
       <c r="E160" s="15" t="s">
-        <v>1061</v>
+        <v>1022</v>
       </c>
       <c r="F160" s="15" t="s">
-        <v>1062</v>
+        <v>1023</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>1063</v>
+        <v>1024</v>
       </c>
       <c r="H160" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I160" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I160" s="15"/>
     </row>
     <row r="161" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B161" s="15" t="s">
-        <v>1064</v>
+        <v>1025</v>
       </c>
       <c r="C161" s="15" t="s">
-        <v>1065</v>
+        <v>1026</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>1066</v>
+        <v>1027</v>
       </c>
       <c r="E161" s="15" t="s">
-        <v>1067</v>
+        <v>1028</v>
       </c>
       <c r="F161" s="15" t="s">
-        <v>1068</v>
+        <v>1029</v>
       </c>
       <c r="G161" s="15" t="s">
-        <v>1069</v>
+        <v>1030</v>
       </c>
       <c r="H161" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I161" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I161" s="15"/>
     </row>
     <row r="162" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B162" s="15" t="s">
-        <v>1070</v>
+        <v>1031</v>
       </c>
       <c r="C162" s="15" t="s">
-        <v>1071</v>
+        <v>1032</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>1072</v>
+        <v>1033</v>
       </c>
       <c r="E162" s="15" t="s">
-        <v>1073</v>
+        <v>1034</v>
       </c>
       <c r="F162" s="15" t="s">
-        <v>1074</v>
+        <v>1035</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>1075</v>
+        <v>1036</v>
       </c>
       <c r="H162" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I162" s="15" t="s">
-        <v>1076</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I162" s="15"/>
     </row>
     <row r="163" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B163" s="15" t="s">
-        <v>1077</v>
+        <v>1037</v>
       </c>
       <c r="C163" s="15" t="s">
-        <v>1078</v>
+        <v>1038</v>
       </c>
       <c r="D163" s="15" t="s">
-        <v>1079</v>
+        <v>1039</v>
       </c>
       <c r="E163" s="15" t="s">
-        <v>1080</v>
+        <v>1040</v>
       </c>
       <c r="F163" s="15" t="s">
-        <v>1081</v>
+        <v>1041</v>
       </c>
       <c r="G163" s="15" t="s">
-        <v>1082</v>
+        <v>1042</v>
       </c>
       <c r="H163" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I163" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I163" s="15"/>
     </row>
     <row r="164" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B164" s="15" t="s">
-        <v>1083</v>
+        <v>1043</v>
       </c>
       <c r="C164" s="15" t="s">
-        <v>1084</v>
+        <v>1044</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>1085</v>
+        <v>1045</v>
       </c>
       <c r="E164" s="15" t="s">
-        <v>1086</v>
+        <v>1046</v>
       </c>
       <c r="F164" s="15" t="s">
-        <v>1087</v>
+        <v>1047</v>
       </c>
       <c r="G164" s="15" t="s">
-        <v>1088</v>
+        <v>1048</v>
       </c>
       <c r="H164" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I164" s="15" t="s">
-        <v>1089</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I164" s="15"/>
     </row>
     <row r="165" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B165" s="15" t="s">
-        <v>1090</v>
+        <v>1049</v>
       </c>
       <c r="C165" s="15" t="s">
-        <v>1091</v>
+        <v>1050</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>1092</v>
+        <v>1051</v>
       </c>
       <c r="E165" s="15" t="s">
-        <v>1093</v>
+        <v>1052</v>
       </c>
       <c r="F165" s="15" t="s">
-        <v>1094</v>
+        <v>1053</v>
       </c>
       <c r="G165" s="15" t="s">
-        <v>1095</v>
+        <v>1054</v>
       </c>
       <c r="H165" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I165" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I165" s="15"/>
     </row>
     <row r="166" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B166" s="15" t="s">
-        <v>1096</v>
+        <v>1055</v>
       </c>
       <c r="C166" s="15" t="s">
-        <v>1097</v>
+        <v>1056</v>
       </c>
       <c r="D166" s="15" t="s">
-        <v>1098</v>
+        <v>1057</v>
       </c>
       <c r="E166" s="15" t="s">
-        <v>1099</v>
+        <v>1058</v>
       </c>
       <c r="F166" s="15" t="s">
-        <v>1100</v>
+        <v>1059</v>
       </c>
       <c r="G166" s="15" t="s">
-        <v>1101</v>
+        <v>1060</v>
       </c>
       <c r="H166" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I166" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I166" s="15"/>
     </row>
     <row r="167" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B167" s="15" t="s">
-        <v>1102</v>
+        <v>1061</v>
       </c>
       <c r="C167" s="15" t="s">
-        <v>1103</v>
+        <v>1062</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>1104</v>
+        <v>1063</v>
       </c>
       <c r="E167" s="15" t="s">
-        <v>1105</v>
+        <v>1064</v>
       </c>
       <c r="F167" s="15" t="s">
-        <v>1106</v>
+        <v>1065</v>
       </c>
       <c r="G167" s="15" t="s">
-        <v>1107</v>
+        <v>1066</v>
       </c>
       <c r="H167" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I167" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I167" s="15"/>
     </row>
     <row r="168" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B168" s="15" t="s">
-        <v>1108</v>
+        <v>1067</v>
       </c>
       <c r="C168" s="15" t="s">
-        <v>1109</v>
+        <v>1068</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>1110</v>
+        <v>1069</v>
       </c>
       <c r="E168" s="15" t="s">
-        <v>1111</v>
+        <v>1070</v>
       </c>
       <c r="F168" s="15" t="s">
-        <v>1112</v>
+        <v>1071</v>
       </c>
       <c r="G168" s="15" t="s">
-        <v>1113</v>
+        <v>1072</v>
       </c>
       <c r="H168" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I168" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I168" s="15"/>
     </row>
     <row r="169" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>1114</v>
+        <v>1073</v>
       </c>
       <c r="C169" s="15" t="s">
-        <v>1115</v>
+        <v>1074</v>
       </c>
       <c r="D169" s="15" t="s">
-        <v>1116</v>
+        <v>1075</v>
       </c>
       <c r="E169" s="15" t="s">
-        <v>1117</v>
+        <v>1076</v>
       </c>
       <c r="F169" s="15" t="s">
-        <v>1118</v>
+        <v>1077</v>
       </c>
       <c r="G169" s="15" t="s">
-        <v>1119</v>
+        <v>1078</v>
       </c>
       <c r="H169" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I169" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I169" s="15"/>
     </row>
     <row r="170" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B170" s="15" t="s">
-        <v>1120</v>
+        <v>1079</v>
       </c>
       <c r="C170" s="15" t="s">
-        <v>1121</v>
+        <v>1080</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>1122</v>
+        <v>1081</v>
       </c>
       <c r="E170" s="15" t="s">
-        <v>1123</v>
+        <v>1082</v>
       </c>
       <c r="F170" s="15" t="s">
-        <v>1124</v>
+        <v>1083</v>
       </c>
       <c r="G170" s="15" t="s">
-        <v>1125</v>
+        <v>1084</v>
       </c>
       <c r="H170" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I170" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I170" s="15"/>
     </row>
     <row r="171" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>1126</v>
+        <v>1085</v>
       </c>
       <c r="C171" s="15" t="s">
-        <v>1127</v>
+        <v>1086</v>
       </c>
       <c r="D171" s="15" t="s">
-        <v>1128</v>
+        <v>1087</v>
       </c>
       <c r="E171" s="15" t="s">
-        <v>1129</v>
+        <v>1088</v>
       </c>
       <c r="F171" s="15" t="s">
-        <v>1130</v>
+        <v>1089</v>
       </c>
       <c r="G171" s="15" t="s">
-        <v>1131</v>
+        <v>1090</v>
       </c>
       <c r="H171" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I171" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I171" s="15"/>
     </row>
     <row r="172" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B172" s="15" t="s">
-        <v>1132</v>
+        <v>1091</v>
       </c>
       <c r="C172" s="15" t="s">
-        <v>1133</v>
+        <v>1092</v>
       </c>
       <c r="D172" s="15" t="s">
-        <v>1134</v>
+        <v>1093</v>
       </c>
       <c r="E172" s="15" t="s">
-        <v>1135</v>
+        <v>1094</v>
       </c>
       <c r="F172" s="15" t="s">
-        <v>1136</v>
+        <v>1095</v>
       </c>
       <c r="G172" s="15" t="s">
-        <v>1137</v>
+        <v>1096</v>
       </c>
       <c r="H172" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I172" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I172" s="15"/>
     </row>
     <row r="173" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>1138</v>
+        <v>1097</v>
       </c>
       <c r="C173" s="15" t="s">
-        <v>1139</v>
+        <v>1098</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>1140</v>
+        <v>1099</v>
       </c>
       <c r="E173" s="15" t="s">
-        <v>1141</v>
+        <v>1100</v>
       </c>
       <c r="F173" s="15" t="s">
-        <v>1142</v>
+        <v>1101</v>
       </c>
       <c r="G173" s="15" t="s">
-        <v>1143</v>
+        <v>1102</v>
       </c>
       <c r="H173" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I173" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I173" s="15"/>
     </row>
     <row r="174" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B174" s="15" t="s">
-        <v>1144</v>
+        <v>1103</v>
       </c>
       <c r="C174" s="15" t="s">
-        <v>1145</v>
+        <v>1104</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>1146</v>
+        <v>1105</v>
       </c>
       <c r="E174" s="15" t="s">
-        <v>1147</v>
+        <v>1106</v>
       </c>
       <c r="F174" s="15" t="s">
-        <v>1148</v>
+        <v>1107</v>
       </c>
       <c r="G174" s="15" t="s">
-        <v>1149</v>
+        <v>1108</v>
       </c>
       <c r="H174" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I174" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I174" s="15"/>
     </row>
     <row r="175" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>1150</v>
+        <v>1109</v>
       </c>
       <c r="C175" s="15" t="s">
-        <v>1151</v>
+        <v>1110</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>1152</v>
+        <v>1111</v>
       </c>
       <c r="E175" s="15" t="s">
-        <v>1153</v>
+        <v>1112</v>
       </c>
       <c r="F175" s="15" t="s">
-        <v>1154</v>
+        <v>1113</v>
       </c>
       <c r="G175" s="15" t="s">
-        <v>1155</v>
+        <v>1114</v>
       </c>
       <c r="H175" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I175" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I175" s="15"/>
     </row>
     <row r="176" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B176" s="15" t="s">
-        <v>1156</v>
+        <v>1115</v>
       </c>
       <c r="C176" s="15" t="s">
-        <v>1157</v>
+        <v>1116</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>1158</v>
+        <v>1117</v>
       </c>
       <c r="E176" s="15" t="s">
-        <v>1159</v>
+        <v>1118</v>
       </c>
       <c r="F176" s="15" t="s">
-        <v>1160</v>
+        <v>1119</v>
       </c>
       <c r="G176" s="15" t="s">
-        <v>1161</v>
+        <v>1120</v>
       </c>
       <c r="H176" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I176" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I176" s="15"/>
     </row>
     <row r="177" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B177" s="15" t="s">
-        <v>1162</v>
+        <v>1121</v>
       </c>
       <c r="C177" s="15" t="s">
-        <v>1163</v>
+        <v>1122</v>
       </c>
       <c r="D177" s="15" t="s">
-        <v>1164</v>
+        <v>1123</v>
       </c>
       <c r="E177" s="15" t="s">
-        <v>1165</v>
+        <v>1124</v>
       </c>
       <c r="F177" s="15" t="s">
-        <v>1166</v>
+        <v>1125</v>
       </c>
       <c r="G177" s="15" t="s">
-        <v>1167</v>
+        <v>1126</v>
       </c>
       <c r="H177" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I177" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I177" s="15"/>
     </row>
     <row r="178" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B178" s="15" t="s">
-        <v>1168</v>
+        <v>1127</v>
       </c>
       <c r="C178" s="15" t="s">
-        <v>1169</v>
+        <v>1128</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>1170</v>
+        <v>1129</v>
       </c>
       <c r="E178" s="15" t="s">
-        <v>1171</v>
+        <v>1130</v>
       </c>
       <c r="F178" s="15" t="s">
-        <v>1172</v>
+        <v>1131</v>
       </c>
       <c r="G178" s="15" t="s">
-        <v>1173</v>
+        <v>1132</v>
       </c>
       <c r="H178" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I178" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I178" s="15"/>
     </row>
     <row r="179" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B179" s="15" t="s">
-        <v>1174</v>
+        <v>1133</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>1175</v>
+        <v>1134</v>
       </c>
       <c r="D179" s="15" t="s">
-        <v>1176</v>
+        <v>1135</v>
       </c>
       <c r="E179" s="15" t="s">
-        <v>1177</v>
+        <v>1136</v>
       </c>
       <c r="F179" s="15" t="s">
-        <v>1178</v>
+        <v>1137</v>
       </c>
       <c r="G179" s="15" t="s">
-        <v>1179</v>
+        <v>1138</v>
       </c>
       <c r="H179" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I179" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I179" s="15"/>
     </row>
     <row r="180" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>1180</v>
+        <v>1139</v>
       </c>
       <c r="C180" s="15" t="s">
-        <v>1181</v>
+        <v>1140</v>
       </c>
       <c r="D180" s="15" t="s">
-        <v>1182</v>
+        <v>1141</v>
       </c>
       <c r="E180" s="15" t="s">
-        <v>1183</v>
+        <v>1142</v>
       </c>
       <c r="F180" s="15" t="s">
-        <v>1184</v>
+        <v>1143</v>
       </c>
       <c r="G180" s="15" t="s">
-        <v>1185</v>
+        <v>1144</v>
       </c>
       <c r="H180" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I180" s="15" t="s">
-        <v>1186</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I180" s="15"/>
     </row>
     <row r="181" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B181" s="15" t="s">
-        <v>1187</v>
+        <v>1145</v>
       </c>
       <c r="C181" s="15" t="s">
-        <v>1188</v>
+        <v>1146</v>
       </c>
       <c r="D181" s="15" t="s">
-        <v>1189</v>
+        <v>1147</v>
       </c>
       <c r="E181" s="15" t="s">
-        <v>1190</v>
+        <v>1148</v>
       </c>
       <c r="F181" s="15" t="s">
-        <v>1191</v>
+        <v>1149</v>
       </c>
       <c r="G181" s="15" t="s">
-        <v>1192</v>
+        <v>1150</v>
       </c>
       <c r="H181" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I181" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I181" s="15"/>
     </row>
     <row r="182" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>1193</v>
+        <v>1151</v>
       </c>
       <c r="C182" s="15" t="s">
-        <v>1194</v>
+        <v>1152</v>
       </c>
       <c r="D182" s="15" t="s">
-        <v>1195</v>
+        <v>1153</v>
       </c>
       <c r="E182" s="15" t="s">
-        <v>1196</v>
+        <v>1154</v>
       </c>
       <c r="F182" s="15" t="s">
-        <v>1197</v>
+        <v>1155</v>
       </c>
       <c r="G182" s="15" t="s">
-        <v>1198</v>
+        <v>1156</v>
       </c>
       <c r="H182" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I182" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I182" s="15"/>
     </row>
     <row r="183" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B183" s="15" t="s">
-        <v>1199</v>
+        <v>1157</v>
       </c>
       <c r="C183" s="15" t="s">
-        <v>1200</v>
+        <v>1158</v>
       </c>
       <c r="D183" s="15" t="s">
-        <v>1201</v>
+        <v>1159</v>
       </c>
       <c r="E183" s="15" t="s">
-        <v>1202</v>
+        <v>1160</v>
       </c>
       <c r="F183" s="15" t="s">
-        <v>1203</v>
+        <v>1161</v>
       </c>
       <c r="G183" s="15" t="s">
-        <v>1204</v>
+        <v>1162</v>
       </c>
       <c r="H183" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I183" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I183" s="15"/>
     </row>
     <row r="184" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B184" s="15" t="s">
-        <v>1205</v>
+        <v>1163</v>
       </c>
       <c r="C184" s="15" t="s">
-        <v>1206</v>
+        <v>1164</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>1207</v>
+        <v>1165</v>
       </c>
       <c r="E184" s="15" t="s">
-        <v>1208</v>
+        <v>1166</v>
       </c>
       <c r="F184" s="15" t="s">
-        <v>1209</v>
+        <v>1167</v>
       </c>
       <c r="G184" s="15" t="s">
-        <v>1210</v>
+        <v>1168</v>
       </c>
       <c r="H184" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I184" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I184" s="15"/>
     </row>
     <row r="185" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B185" s="15" t="s">
-        <v>1211</v>
+        <v>1169</v>
       </c>
       <c r="C185" s="15" t="s">
-        <v>1212</v>
+        <v>1170</v>
       </c>
       <c r="D185" s="15" t="s">
-        <v>1213</v>
+        <v>1171</v>
       </c>
       <c r="E185" s="15" t="s">
-        <v>1214</v>
+        <v>1172</v>
       </c>
       <c r="F185" s="15" t="s">
-        <v>1215</v>
+        <v>1173</v>
       </c>
       <c r="G185" s="15" t="s">
-        <v>1216</v>
+        <v>1174</v>
       </c>
       <c r="H185" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I185" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I185" s="15"/>
     </row>
     <row r="186" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B186" s="15" t="s">
-        <v>1217</v>
+        <v>1175</v>
       </c>
       <c r="C186" s="15" t="s">
-        <v>1218</v>
+        <v>1176</v>
       </c>
       <c r="D186" s="15" t="s">
-        <v>1219</v>
+        <v>1177</v>
       </c>
       <c r="E186" s="15" t="s">
-        <v>1220</v>
+        <v>1178</v>
       </c>
       <c r="F186" s="15" t="s">
-        <v>1221</v>
+        <v>1179</v>
       </c>
       <c r="G186" s="15" t="s">
-        <v>1222</v>
+        <v>1180</v>
       </c>
       <c r="H186" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I186" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I186" s="15"/>
     </row>
     <row r="187" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B187" s="15" t="s">
-        <v>1223</v>
+        <v>1181</v>
       </c>
       <c r="C187" s="15" t="s">
-        <v>1224</v>
+        <v>1182</v>
       </c>
       <c r="D187" s="15" t="s">
-        <v>1225</v>
+        <v>1183</v>
       </c>
       <c r="E187" s="15" t="s">
-        <v>1226</v>
+        <v>1184</v>
       </c>
       <c r="F187" s="15" t="s">
-        <v>1227</v>
+        <v>1185</v>
       </c>
       <c r="G187" s="15" t="s">
-        <v>1228</v>
+        <v>1186</v>
       </c>
       <c r="H187" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I187" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I187" s="15"/>
     </row>
     <row r="188" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B188" s="15" t="s">
-        <v>1229</v>
+        <v>1187</v>
       </c>
       <c r="C188" s="15" t="s">
-        <v>1230</v>
+        <v>1188</v>
       </c>
       <c r="D188" s="15" t="s">
-        <v>1231</v>
+        <v>1189</v>
       </c>
       <c r="E188" s="15" t="s">
-        <v>1232</v>
+        <v>1190</v>
       </c>
       <c r="F188" s="15" t="s">
-        <v>1233</v>
+        <v>1191</v>
       </c>
       <c r="G188" s="15" t="s">
-        <v>1234</v>
+        <v>1192</v>
       </c>
       <c r="H188" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I188" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I188" s="15"/>
     </row>
     <row r="189" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B189" s="15" t="s">
-        <v>1235</v>
+        <v>1193</v>
       </c>
       <c r="C189" s="15" t="s">
-        <v>1236</v>
+        <v>1194</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>1237</v>
+        <v>1195</v>
       </c>
       <c r="E189" s="15" t="s">
-        <v>1238</v>
+        <v>1196</v>
       </c>
       <c r="F189" s="15" t="s">
-        <v>1239</v>
+        <v>1197</v>
       </c>
       <c r="G189" s="15" t="s">
-        <v>1240</v>
+        <v>1198</v>
       </c>
       <c r="H189" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I189" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I189" s="15"/>
     </row>
     <row r="190" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B190" s="15" t="s">
-        <v>1241</v>
+        <v>1199</v>
       </c>
       <c r="C190" s="15" t="s">
-        <v>1242</v>
+        <v>1200</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>1243</v>
+        <v>1201</v>
       </c>
       <c r="E190" s="15" t="s">
-        <v>1244</v>
+        <v>1202</v>
       </c>
       <c r="F190" s="15" t="s">
-        <v>1245</v>
+        <v>1203</v>
       </c>
       <c r="G190" s="15" t="s">
-        <v>1246</v>
+        <v>1204</v>
       </c>
       <c r="H190" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I190" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I190" s="15"/>
     </row>
     <row r="191" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B191" s="15" t="s">
-        <v>1247</v>
+        <v>1205</v>
       </c>
       <c r="C191" s="15" t="s">
-        <v>1248</v>
+        <v>1206</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>1249</v>
+        <v>1207</v>
       </c>
       <c r="E191" s="15" t="s">
-        <v>1250</v>
+        <v>1208</v>
       </c>
       <c r="F191" s="15" t="s">
-        <v>1251</v>
+        <v>1209</v>
       </c>
       <c r="G191" s="15" t="s">
-        <v>1252</v>
+        <v>1210</v>
       </c>
       <c r="H191" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I191" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I191" s="15"/>
     </row>
     <row r="192" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B192" s="15" t="s">
-        <v>1253</v>
+        <v>1211</v>
       </c>
       <c r="C192" s="15" t="s">
-        <v>1254</v>
+        <v>1212</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>1255</v>
+        <v>1213</v>
       </c>
       <c r="E192" s="15" t="s">
-        <v>1256</v>
+        <v>1214</v>
       </c>
       <c r="F192" s="15" t="s">
-        <v>1257</v>
+        <v>1215</v>
       </c>
       <c r="G192" s="15" t="s">
-        <v>1258</v>
+        <v>1216</v>
       </c>
       <c r="H192" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I192" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I192" s="15"/>
     </row>
     <row r="193" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B193" s="15" t="s">
-        <v>1259</v>
+        <v>1217</v>
       </c>
       <c r="C193" s="15" t="s">
-        <v>1260</v>
+        <v>1218</v>
       </c>
       <c r="D193" s="15" t="s">
-        <v>1261</v>
+        <v>1219</v>
       </c>
       <c r="E193" s="15" t="s">
-        <v>1262</v>
+        <v>1220</v>
       </c>
       <c r="F193" s="15" t="s">
-        <v>1263</v>
+        <v>1221</v>
       </c>
       <c r="G193" s="15" t="s">
-        <v>1264</v>
+        <v>1222</v>
       </c>
       <c r="H193" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I193" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I193" s="15"/>
     </row>
     <row r="194" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B194" s="15" t="s">
-        <v>1265</v>
+        <v>1223</v>
       </c>
       <c r="C194" s="15" t="s">
-        <v>1266</v>
+        <v>1224</v>
       </c>
       <c r="D194" s="15" t="s">
-        <v>1267</v>
+        <v>1225</v>
       </c>
       <c r="E194" s="15" t="s">
-        <v>1268</v>
+        <v>1226</v>
       </c>
       <c r="F194" s="15" t="s">
-        <v>1269</v>
+        <v>1227</v>
       </c>
       <c r="G194" s="15" t="s">
-        <v>1270</v>
+        <v>1228</v>
       </c>
       <c r="H194" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I194" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I194" s="15"/>
     </row>
     <row r="195" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B195" s="15" t="s">
-        <v>1271</v>
+        <v>1229</v>
       </c>
       <c r="C195" s="15" t="s">
-        <v>1272</v>
+        <v>1230</v>
       </c>
       <c r="D195" s="15" t="s">
-        <v>1273</v>
+        <v>1231</v>
       </c>
       <c r="E195" s="15" t="s">
-        <v>1274</v>
+        <v>1232</v>
       </c>
       <c r="F195" s="15" t="s">
-        <v>1275</v>
+        <v>1233</v>
       </c>
       <c r="G195" s="15" t="s">
-        <v>1276</v>
+        <v>1234</v>
       </c>
       <c r="H195" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I195" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I195" s="15"/>
     </row>
     <row r="196" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B196" s="15" t="s">
-        <v>1277</v>
+        <v>1235</v>
       </c>
       <c r="C196" s="15" t="s">
-        <v>1278</v>
+        <v>1236</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>1279</v>
+        <v>1237</v>
       </c>
       <c r="E196" s="15" t="s">
-        <v>1280</v>
+        <v>1238</v>
       </c>
       <c r="F196" s="15" t="s">
-        <v>1281</v>
+        <v>1239</v>
       </c>
       <c r="G196" s="15" t="s">
-        <v>1282</v>
+        <v>1240</v>
       </c>
       <c r="H196" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I196" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I196" s="15"/>
     </row>
     <row r="197" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B197" s="15" t="s">
-        <v>1283</v>
+        <v>1241</v>
       </c>
       <c r="C197" s="15" t="s">
-        <v>1284</v>
+        <v>1242</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>1285</v>
+        <v>1243</v>
       </c>
       <c r="E197" s="15" t="s">
-        <v>1286</v>
+        <v>1244</v>
       </c>
       <c r="F197" s="15" t="s">
-        <v>1287</v>
+        <v>1245</v>
       </c>
       <c r="G197" s="15" t="s">
-        <v>1288</v>
+        <v>1246</v>
       </c>
       <c r="H197" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I197" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I197" s="15"/>
     </row>
     <row r="198" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B198" s="15" t="s">
-        <v>1289</v>
+        <v>1247</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>1290</v>
+        <v>1248</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>1291</v>
+        <v>1249</v>
       </c>
       <c r="E198" s="15" t="s">
-        <v>1292</v>
+        <v>1250</v>
       </c>
       <c r="F198" s="15" t="s">
-        <v>1293</v>
+        <v>1251</v>
       </c>
       <c r="G198" s="15" t="s">
-        <v>1294</v>
+        <v>1252</v>
       </c>
       <c r="H198" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I198" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I198" s="15"/>
     </row>
     <row r="199" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B199" s="15" t="s">
-        <v>1295</v>
+        <v>1253</v>
       </c>
       <c r="C199" s="15" t="s">
-        <v>1296</v>
+        <v>1254</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>1297</v>
+        <v>1255</v>
       </c>
       <c r="E199" s="15" t="s">
-        <v>1298</v>
+        <v>1256</v>
       </c>
       <c r="F199" s="15" t="s">
-        <v>1299</v>
+        <v>1257</v>
       </c>
       <c r="G199" s="15" t="s">
-        <v>1300</v>
+        <v>1258</v>
       </c>
       <c r="H199" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I199" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I199" s="15"/>
     </row>
     <row r="200" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B200" s="15" t="s">
-        <v>1301</v>
+        <v>1259</v>
       </c>
       <c r="C200" s="15" t="s">
-        <v>1302</v>
+        <v>1260</v>
       </c>
       <c r="D200" s="15" t="s">
-        <v>1303</v>
+        <v>1261</v>
       </c>
       <c r="E200" s="15" t="s">
-        <v>1304</v>
+        <v>1262</v>
       </c>
       <c r="F200" s="15" t="s">
-        <v>1305</v>
+        <v>1263</v>
       </c>
       <c r="G200" s="15" t="s">
-        <v>1306</v>
+        <v>1264</v>
       </c>
       <c r="H200" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I200" s="15" t="s">
-        <v>1307</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I200" s="15"/>
     </row>
     <row r="201" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B201" s="15" t="s">
-        <v>1308</v>
+        <v>1265</v>
       </c>
       <c r="C201" s="15" t="s">
-        <v>1309</v>
+        <v>1266</v>
       </c>
       <c r="D201" s="15" t="s">
-        <v>1310</v>
+        <v>1267</v>
       </c>
       <c r="E201" s="15" t="s">
-        <v>1311</v>
+        <v>1268</v>
       </c>
       <c r="F201" s="15" t="s">
-        <v>1312</v>
+        <v>1269</v>
       </c>
       <c r="G201" s="15" t="s">
-        <v>1313</v>
+        <v>1270</v>
       </c>
       <c r="H201" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="I201" s="15" t="s">
-        <v>78</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="I201" s="15"/>
     </row>
   </sheetData>
   <dataValidations count="2">
